--- a/assets/Listados/CGS - 3414937 - 2026.xlsx
+++ b/assets/Listados/CGS - 3414937 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C241FFCC-B929-4535-AD5A-E80B885346F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE51A8C2-4133-416D-8D25-9ECE7114E203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="365">
   <si>
     <r>
       <rPr>
@@ -1194,12 +1194,6 @@
     <t>Pereira Ávila</t>
   </si>
   <si>
-    <t xml:space="preserve">Sharith Yesid </t>
-  </si>
-  <si>
-    <t>González Rodríguez</t>
-  </si>
-  <si>
     <t>Danna Nicol</t>
   </si>
   <si>
@@ -1324,6 +1318,9 @@
   </si>
   <si>
     <t xml:space="preserve">Delicias de Amor </t>
+  </si>
+  <si>
+    <t>Budusitos</t>
   </si>
 </sst>
 </file>
@@ -2767,7 +2764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3295,6 +3292,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -42446,13 +42446,13 @@
         <v>32</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D9" s="58" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>72</v>
@@ -42467,13 +42467,13 @@
         <v>75</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J9" s="58" t="s">
         <v>76</v>
       </c>
       <c r="K9" s="58" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -43211,7 +43211,7 @@
       </c>
       <c r="L24" s="48"/>
       <c r="M24" s="48" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N24" s="48"/>
       <c r="O24" s="48"/>
@@ -43251,7 +43251,7 @@
       <c r="H25" s="84" t="s">
         <v>205</v>
       </c>
-      <c r="I25" s="82" t="s">
+      <c r="I25" s="214" t="s">
         <v>206</v>
       </c>
       <c r="J25" s="82">
@@ -43380,7 +43380,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C28" s="95" t="s">
         <v>126</v>
@@ -43458,7 +43458,7 @@
       </c>
       <c r="L29" s="48"/>
       <c r="M29" s="48" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N29" s="48"/>
       <c r="O29" s="48"/>
@@ -44097,7 +44097,7 @@
       </c>
       <c r="L42" s="48"/>
       <c r="M42" s="48" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N42" s="48"/>
       <c r="O42" s="48"/>
@@ -44148,7 +44148,7 @@
       </c>
       <c r="L43" s="48"/>
       <c r="M43" s="48" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N43" s="48"/>
       <c r="O43" s="48"/>
@@ -53011,11 +53011,12 @@
     <hyperlink ref="F39" r:id="rId71" xr:uid="{47CB2AD8-9FEB-42DA-94CA-F35FFA40E3FF}"/>
     <hyperlink ref="F22" r:id="rId72" xr:uid="{21AC6427-A11A-4A46-ACA5-32AE00815FCB}"/>
     <hyperlink ref="F40" r:id="rId73" xr:uid="{4F07F6D4-EEEA-444E-9ABD-73F7C92C1243}"/>
+    <hyperlink ref="I25" r:id="rId74" xr:uid="{FC0A317B-27AA-4EC1-8D42-4C7FE00C723E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId74"/>
+  <pageSetup orientation="landscape" r:id="rId75"/>
   <tableParts count="1">
-    <tablePart r:id="rId75"/>
+    <tablePart r:id="rId76"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -53072,7 +53073,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.75">
       <c r="A3" s="210" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>275</v>
@@ -53145,7 +53146,7 @@
     </row>
     <row r="10" spans="1:6" ht="15.75">
       <c r="A10" s="210" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B10" s="66" t="s">
         <v>284</v>
@@ -53172,26 +53173,20 @@
     <row r="12" spans="1:6" ht="15.75">
       <c r="A12" s="211"/>
       <c r="B12" s="66" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
       <c r="A13" s="211"/>
-      <c r="B13" s="66" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="66" t="s">
-        <v>292</v>
-      </c>
-      <c r="D13" s="113" t="s">
-        <v>158</v>
-      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="113"/>
     </row>
     <row r="14" spans="1:6" ht="15.75">
       <c r="A14" s="212"/>
@@ -53215,7 +53210,7 @@
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="210" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B17" s="66" t="s">
         <v>293</v>
@@ -53285,7 +53280,7 @@
     </row>
     <row r="24" spans="1:4" ht="15.75">
       <c r="A24" s="210" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B24" s="66" t="s">
         <v>302</v>
@@ -53315,7 +53310,7 @@
         <v>306</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D26" s="113" t="s">
         <v>131</v>
@@ -53355,7 +53350,7 @@
     </row>
     <row r="31" spans="1:4" ht="15.75">
       <c r="A31" s="210" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B31" s="66" t="s">
         <v>309</v>
@@ -53425,7 +53420,7 @@
     </row>
     <row r="38" spans="1:4" ht="15.75">
       <c r="A38" s="210" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B38" s="66" t="s">
         <v>317</v>
@@ -53443,7 +53438,7 @@
         <v>319</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D39" s="113" t="s">
         <v>143</v>
@@ -53464,13 +53459,13 @@
     <row r="41" spans="1:4" ht="15.75">
       <c r="A41" s="211"/>
       <c r="B41" s="66" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="D41" s="113" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
@@ -53496,13 +53491,13 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
       <c r="A45" s="210" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B45" s="66" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C45" s="66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D45" s="113" t="s">
         <v>133</v>
@@ -53511,10 +53506,10 @@
     <row r="46" spans="1:4" ht="15" customHeight="1">
       <c r="A46" s="211"/>
       <c r="B46" s="66" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C46" s="66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D46" s="113" t="s">
         <v>146</v>
@@ -53523,10 +53518,10 @@
     <row r="47" spans="1:4" ht="15" customHeight="1">
       <c r="A47" s="211"/>
       <c r="B47" s="66" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C47" s="66" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D47" s="113" t="s">
         <v>140</v>
@@ -53535,10 +53530,10 @@
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="211"/>
       <c r="B48" s="66" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C48" s="66" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D48" s="113" t="s">
         <v>135</v>
@@ -53567,13 +53562,13 @@
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
       <c r="A52" s="210" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B52" s="66" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C52" s="66" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D52" s="113" t="s">
         <v>136</v>
@@ -53582,10 +53577,10 @@
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="211"/>
       <c r="B53" s="66" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C53" s="66" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D53" s="113" t="s">
         <v>150</v>
@@ -53594,10 +53589,10 @@
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="211"/>
       <c r="B54" s="66" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="66" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D54" s="113" t="s">
         <v>148</v>
@@ -53606,10 +53601,10 @@
     <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="211"/>
       <c r="B55" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="C55" s="66" t="s">
         <v>338</v>
-      </c>
-      <c r="C55" s="66" t="s">
-        <v>340</v>
       </c>
       <c r="D55" s="113" t="s">
         <v>144</v>
@@ -53618,10 +53613,10 @@
     <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A56" s="212"/>
       <c r="B56" s="68" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C56" s="68" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D56" s="118" t="s">
         <v>155</v>
@@ -53643,12 +53638,14 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="210"/>
+      <c r="A59" s="210" t="s">
+        <v>364</v>
+      </c>
       <c r="B59" s="66" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C59" s="66" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D59" s="113" t="s">
         <v>138</v>
@@ -53657,10 +53654,10 @@
     <row r="60" spans="1:4" ht="15" customHeight="1">
       <c r="A60" s="211"/>
       <c r="B60" s="66" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C60" s="66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D60" s="113" t="s">
         <v>156</v>
@@ -53704,35 +53701,34 @@
     <hyperlink ref="D6" r:id="rId4" xr:uid="{D14A4E92-C0E2-4696-BF8F-D8F4C20394FC}"/>
     <hyperlink ref="D10" r:id="rId5" xr:uid="{7598D655-2180-461C-9928-8BE1BFC7DC83}"/>
     <hyperlink ref="D11" r:id="rId6" xr:uid="{D5C00FFE-C863-4926-9205-AF8F08BEC239}"/>
-    <hyperlink ref="D12" r:id="rId7" xr:uid="{564CB0C5-9294-43C8-9F74-758633B923E8}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{287BD786-4DED-4DBF-B6F3-AF9F422314C2}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{E29BFCDD-27C7-4BBA-82F1-8DA1BB4BF5E0}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{AF6534E7-3696-4873-84C8-6037A9BB6F8C}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{335FE742-65B9-4738-B90A-0917A8AE3738}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{D00ABF86-B5B6-4CF2-834B-208EB25AC884}"/>
-    <hyperlink ref="D24" r:id="rId13" xr:uid="{7EAB6215-249B-444D-9E1E-C71E6A387E5B}"/>
-    <hyperlink ref="D25" r:id="rId14" xr:uid="{1EEC0362-69F4-4457-9702-49517EF9B022}"/>
-    <hyperlink ref="D26" r:id="rId15" xr:uid="{836C440A-F077-4AE0-A519-1A7D133A6DA5}"/>
-    <hyperlink ref="D27" r:id="rId16" xr:uid="{62EB46EE-231C-4953-9AE3-D9DD2AD48658}"/>
-    <hyperlink ref="D31" r:id="rId17" xr:uid="{840E8B01-D584-4103-BCDC-1087897CD79F}"/>
-    <hyperlink ref="D32" r:id="rId18" xr:uid="{48F22200-13AE-4713-AE5B-423F84F70075}"/>
-    <hyperlink ref="D33" r:id="rId19" xr:uid="{1AC3C72B-2911-40D8-9DF1-A116DF0A84BC}"/>
-    <hyperlink ref="D34" r:id="rId20" xr:uid="{F0DAA9D4-4B78-4B96-A1F3-86171AEB6763}"/>
-    <hyperlink ref="D38" r:id="rId21" xr:uid="{525CC6A7-E041-40D7-890B-B8625400678D}"/>
-    <hyperlink ref="D39" r:id="rId22" xr:uid="{F2007303-9E1D-45D2-A959-97CE8081C45E}"/>
-    <hyperlink ref="D40" r:id="rId23" xr:uid="{634ED716-CF7B-45CA-939A-B631D3D6C0C0}"/>
-    <hyperlink ref="D41" r:id="rId24" xr:uid="{ACDFB16E-EFCD-4208-905F-72D0BE4233B4}"/>
-    <hyperlink ref="D45" r:id="rId25" xr:uid="{85A134AC-87E3-4A71-8F8B-2218D89B1CF7}"/>
-    <hyperlink ref="D46" r:id="rId26" xr:uid="{55BD9931-A487-4129-B613-D052B9D2E43A}"/>
-    <hyperlink ref="D47" r:id="rId27" xr:uid="{6E9F97FA-3140-4E41-A8BD-C7E8D3F86C7B}"/>
-    <hyperlink ref="D48" r:id="rId28" xr:uid="{0472DDC2-CBD4-4B04-8528-EA9BBA75F391}"/>
-    <hyperlink ref="D52" r:id="rId29" xr:uid="{10C1359B-FE2B-41CE-99BF-90A20059629F}"/>
-    <hyperlink ref="D53" r:id="rId30" xr:uid="{8AE6A0A2-716A-46F8-8441-68E9607A39C7}"/>
-    <hyperlink ref="D54" r:id="rId31" xr:uid="{D79013BE-C6A2-439D-9836-1E180BA23CBB}"/>
-    <hyperlink ref="D55" r:id="rId32" xr:uid="{75D666DD-10EC-4262-B05C-5B12DCA9EAC5}"/>
-    <hyperlink ref="D56" r:id="rId33" xr:uid="{EB07EF50-4E64-43BA-87CD-BB81127CCCB7}"/>
-    <hyperlink ref="D59" r:id="rId34" xr:uid="{80B3C828-94C9-4BC4-BFDA-AFE5E3F5B574}"/>
-    <hyperlink ref="D60" r:id="rId35" xr:uid="{BA2F860E-577E-42F3-A716-4F537F1889D0}"/>
+    <hyperlink ref="D17" r:id="rId7" xr:uid="{E29BFCDD-27C7-4BBA-82F1-8DA1BB4BF5E0}"/>
+    <hyperlink ref="D18" r:id="rId8" xr:uid="{AF6534E7-3696-4873-84C8-6037A9BB6F8C}"/>
+    <hyperlink ref="D19" r:id="rId9" xr:uid="{335FE742-65B9-4738-B90A-0917A8AE3738}"/>
+    <hyperlink ref="D20" r:id="rId10" xr:uid="{D00ABF86-B5B6-4CF2-834B-208EB25AC884}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{7EAB6215-249B-444D-9E1E-C71E6A387E5B}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{1EEC0362-69F4-4457-9702-49517EF9B022}"/>
+    <hyperlink ref="D26" r:id="rId13" xr:uid="{836C440A-F077-4AE0-A519-1A7D133A6DA5}"/>
+    <hyperlink ref="D27" r:id="rId14" xr:uid="{62EB46EE-231C-4953-9AE3-D9DD2AD48658}"/>
+    <hyperlink ref="D31" r:id="rId15" xr:uid="{840E8B01-D584-4103-BCDC-1087897CD79F}"/>
+    <hyperlink ref="D32" r:id="rId16" xr:uid="{48F22200-13AE-4713-AE5B-423F84F70075}"/>
+    <hyperlink ref="D33" r:id="rId17" xr:uid="{1AC3C72B-2911-40D8-9DF1-A116DF0A84BC}"/>
+    <hyperlink ref="D34" r:id="rId18" xr:uid="{F0DAA9D4-4B78-4B96-A1F3-86171AEB6763}"/>
+    <hyperlink ref="D38" r:id="rId19" xr:uid="{525CC6A7-E041-40D7-890B-B8625400678D}"/>
+    <hyperlink ref="D39" r:id="rId20" xr:uid="{F2007303-9E1D-45D2-A959-97CE8081C45E}"/>
+    <hyperlink ref="D40" r:id="rId21" xr:uid="{634ED716-CF7B-45CA-939A-B631D3D6C0C0}"/>
+    <hyperlink ref="D45" r:id="rId22" xr:uid="{85A134AC-87E3-4A71-8F8B-2218D89B1CF7}"/>
+    <hyperlink ref="D46" r:id="rId23" xr:uid="{55BD9931-A487-4129-B613-D052B9D2E43A}"/>
+    <hyperlink ref="D47" r:id="rId24" xr:uid="{6E9F97FA-3140-4E41-A8BD-C7E8D3F86C7B}"/>
+    <hyperlink ref="D48" r:id="rId25" xr:uid="{0472DDC2-CBD4-4B04-8528-EA9BBA75F391}"/>
+    <hyperlink ref="D52" r:id="rId26" xr:uid="{10C1359B-FE2B-41CE-99BF-90A20059629F}"/>
+    <hyperlink ref="D53" r:id="rId27" xr:uid="{8AE6A0A2-716A-46F8-8441-68E9607A39C7}"/>
+    <hyperlink ref="D54" r:id="rId28" xr:uid="{D79013BE-C6A2-439D-9836-1E180BA23CBB}"/>
+    <hyperlink ref="D55" r:id="rId29" xr:uid="{75D666DD-10EC-4262-B05C-5B12DCA9EAC5}"/>
+    <hyperlink ref="D56" r:id="rId30" xr:uid="{EB07EF50-4E64-43BA-87CD-BB81127CCCB7}"/>
+    <hyperlink ref="D59" r:id="rId31" xr:uid="{80B3C828-94C9-4BC4-BFDA-AFE5E3F5B574}"/>
+    <hyperlink ref="D60" r:id="rId32" xr:uid="{BA2F860E-577E-42F3-A716-4F537F1889D0}"/>
+    <hyperlink ref="D41" r:id="rId33" xr:uid="{2D726380-94CC-4CC1-AEB9-3D1F39E2F42D}"/>
+    <hyperlink ref="D12" r:id="rId34" xr:uid="{48A14C87-A122-4450-B388-7FDC011AEB35}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>

--- a/assets/Listados/CGS - 3414937 - 2026.xlsx
+++ b/assets/Listados/CGS - 3414937 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE51A8C2-4133-416D-8D25-9ECE7114E203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB5693-EC90-4B0F-8986-ACFDF6794C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="365">
   <si>
     <r>
       <rPr>
@@ -1748,7 +1748,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1848,6 +1848,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2764,7 +2770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3076,84 +3082,26 @@
     <xf numFmtId="0" fontId="56" fillId="17" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3162,17 +3110,77 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3186,80 +3194,93 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3273,29 +3294,24 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="16" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4738,125 +4754,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="193"/>
-      <c r="B1" s="194"/>
-      <c r="C1" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="173" t="s">
+      <c r="A1" s="158"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="177"/>
-      <c r="T1" s="181"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="182"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="181"/>
-      <c r="AC1" s="122"/>
-      <c r="AD1" s="122"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="122"/>
-      <c r="AG1" s="122"/>
-      <c r="AH1" s="122"/>
-      <c r="AI1" s="122"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="121"/>
-      <c r="AM1" s="122"/>
-      <c r="AN1" s="122"/>
-      <c r="AO1" s="122"/>
-      <c r="AP1" s="122"/>
-      <c r="AQ1" s="122"/>
-      <c r="AR1" s="122"/>
-      <c r="AS1" s="122"/>
-      <c r="AT1" s="122"/>
-      <c r="AU1" s="123"/>
-      <c r="AV1" s="122"/>
-      <c r="AW1" s="122"/>
-      <c r="AX1" s="122"/>
-      <c r="AY1" s="122"/>
-      <c r="AZ1" s="122"/>
-      <c r="BA1" s="122"/>
-      <c r="BB1" s="122"/>
-      <c r="BC1" s="122"/>
-      <c r="BD1" s="122"/>
-      <c r="BE1" s="122"/>
-      <c r="BF1" s="122"/>
-      <c r="BG1" s="122"/>
-      <c r="BH1" s="122"/>
-      <c r="BI1" s="122"/>
-      <c r="BJ1" s="122"/>
-      <c r="BK1" s="122"/>
-      <c r="BL1" s="122"/>
-      <c r="BM1" s="122"/>
-      <c r="BN1" s="122"/>
-      <c r="BO1" s="122"/>
-      <c r="BP1" s="122"/>
-      <c r="BQ1" s="122"/>
-      <c r="BR1" s="122"/>
-      <c r="BS1" s="122"/>
-      <c r="BT1" s="122"/>
-      <c r="BU1" s="122"/>
-      <c r="BV1" s="124"/>
-      <c r="BW1" s="122"/>
-      <c r="BX1" s="122"/>
-      <c r="BY1" s="122"/>
-      <c r="BZ1" s="122"/>
-      <c r="CA1" s="122"/>
-      <c r="CB1" s="122"/>
-      <c r="CC1" s="122"/>
-      <c r="CD1" s="122"/>
-      <c r="CE1" s="122"/>
-      <c r="CF1" s="122"/>
-      <c r="CG1" s="122"/>
-      <c r="CH1" s="122"/>
-      <c r="CI1" s="122"/>
-      <c r="CJ1" s="122"/>
-      <c r="CK1" s="122"/>
-      <c r="CL1" s="122"/>
-      <c r="CM1" s="122"/>
-      <c r="CN1" s="122"/>
-      <c r="CO1" s="122"/>
-      <c r="CP1" s="122"/>
-      <c r="CQ1" s="122"/>
-      <c r="CR1" s="125"/>
-      <c r="CS1" s="128" t="s">
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="162"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="138"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="138"/>
+      <c r="AB1" s="139"/>
+      <c r="AC1" s="138"/>
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="138"/>
+      <c r="AG1" s="138"/>
+      <c r="AH1" s="138"/>
+      <c r="AI1" s="138"/>
+      <c r="AJ1" s="138"/>
+      <c r="AK1" s="140"/>
+      <c r="AL1" s="190"/>
+      <c r="AM1" s="138"/>
+      <c r="AN1" s="138"/>
+      <c r="AO1" s="138"/>
+      <c r="AP1" s="138"/>
+      <c r="AQ1" s="138"/>
+      <c r="AR1" s="138"/>
+      <c r="AS1" s="138"/>
+      <c r="AT1" s="138"/>
+      <c r="AU1" s="191"/>
+      <c r="AV1" s="138"/>
+      <c r="AW1" s="138"/>
+      <c r="AX1" s="138"/>
+      <c r="AY1" s="138"/>
+      <c r="AZ1" s="138"/>
+      <c r="BA1" s="138"/>
+      <c r="BB1" s="138"/>
+      <c r="BC1" s="138"/>
+      <c r="BD1" s="138"/>
+      <c r="BE1" s="138"/>
+      <c r="BF1" s="138"/>
+      <c r="BG1" s="138"/>
+      <c r="BH1" s="138"/>
+      <c r="BI1" s="138"/>
+      <c r="BJ1" s="138"/>
+      <c r="BK1" s="138"/>
+      <c r="BL1" s="138"/>
+      <c r="BM1" s="138"/>
+      <c r="BN1" s="138"/>
+      <c r="BO1" s="138"/>
+      <c r="BP1" s="138"/>
+      <c r="BQ1" s="138"/>
+      <c r="BR1" s="138"/>
+      <c r="BS1" s="138"/>
+      <c r="BT1" s="138"/>
+      <c r="BU1" s="138"/>
+      <c r="BV1" s="192"/>
+      <c r="BW1" s="138"/>
+      <c r="BX1" s="138"/>
+      <c r="BY1" s="138"/>
+      <c r="BZ1" s="138"/>
+      <c r="CA1" s="138"/>
+      <c r="CB1" s="138"/>
+      <c r="CC1" s="138"/>
+      <c r="CD1" s="138"/>
+      <c r="CE1" s="138"/>
+      <c r="CF1" s="138"/>
+      <c r="CG1" s="138"/>
+      <c r="CH1" s="138"/>
+      <c r="CI1" s="138"/>
+      <c r="CJ1" s="138"/>
+      <c r="CK1" s="138"/>
+      <c r="CL1" s="138"/>
+      <c r="CM1" s="138"/>
+      <c r="CN1" s="138"/>
+      <c r="CO1" s="138"/>
+      <c r="CP1" s="138"/>
+      <c r="CQ1" s="138"/>
+      <c r="CR1" s="140"/>
+      <c r="CS1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="129"/>
-      <c r="CU1" s="129"/>
-      <c r="CV1" s="129"/>
-      <c r="CW1" s="130"/>
+      <c r="CT1" s="195"/>
+      <c r="CU1" s="195"/>
+      <c r="CV1" s="195"/>
+      <c r="CW1" s="196"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="145" t="s">
+      <c r="CY1" s="184" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="132"/>
-      <c r="DA1" s="132"/>
-      <c r="DB1" s="132"/>
-      <c r="DC1" s="132"/>
-      <c r="DD1" s="132"/>
-      <c r="DE1" s="132"/>
-      <c r="DF1" s="132"/>
-      <c r="DG1" s="132"/>
+      <c r="CZ1" s="185"/>
+      <c r="DA1" s="185"/>
+      <c r="DB1" s="185"/>
+      <c r="DC1" s="185"/>
+      <c r="DD1" s="185"/>
+      <c r="DE1" s="185"/>
+      <c r="DF1" s="185"/>
+      <c r="DG1" s="185"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4875,111 +4891,111 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="195"/>
-      <c r="B2" s="196"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="173" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="174"/>
-      <c r="Q2" s="175"/>
-      <c r="R2" s="175"/>
-      <c r="S2" s="175"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="139"/>
-      <c r="X2" s="141"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="183"/>
-      <c r="AC2" s="127"/>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="127"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
-      <c r="AI2" s="127"/>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="139"/>
-      <c r="AL2" s="141"/>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="127"/>
-      <c r="AT2" s="127"/>
-      <c r="AU2" s="137"/>
-      <c r="AV2" s="127"/>
-      <c r="AW2" s="127"/>
-      <c r="AX2" s="127"/>
-      <c r="AY2" s="127"/>
-      <c r="AZ2" s="127"/>
-      <c r="BA2" s="127"/>
-      <c r="BB2" s="127"/>
-      <c r="BC2" s="127"/>
-      <c r="BD2" s="127"/>
-      <c r="BE2" s="127"/>
-      <c r="BF2" s="127"/>
-      <c r="BG2" s="127"/>
-      <c r="BH2" s="127"/>
-      <c r="BI2" s="127"/>
-      <c r="BJ2" s="127"/>
-      <c r="BK2" s="127"/>
-      <c r="BL2" s="127"/>
-      <c r="BM2" s="127"/>
-      <c r="BN2" s="127"/>
-      <c r="BO2" s="127"/>
-      <c r="BP2" s="127"/>
-      <c r="BQ2" s="127"/>
-      <c r="BR2" s="127"/>
-      <c r="BS2" s="127"/>
-      <c r="BT2" s="127"/>
-      <c r="BU2" s="127"/>
-      <c r="BV2" s="138"/>
-      <c r="BW2" s="127"/>
-      <c r="BX2" s="127"/>
-      <c r="BY2" s="127"/>
-      <c r="BZ2" s="127"/>
-      <c r="CA2" s="127"/>
-      <c r="CB2" s="127"/>
-      <c r="CC2" s="127"/>
-      <c r="CD2" s="127"/>
-      <c r="CE2" s="127"/>
-      <c r="CF2" s="127"/>
-      <c r="CG2" s="127"/>
-      <c r="CH2" s="127"/>
-      <c r="CI2" s="127"/>
-      <c r="CJ2" s="127"/>
-      <c r="CK2" s="127"/>
-      <c r="CL2" s="127"/>
-      <c r="CM2" s="127"/>
-      <c r="CN2" s="127"/>
-      <c r="CO2" s="127"/>
-      <c r="CP2" s="127"/>
-      <c r="CQ2" s="127"/>
-      <c r="CR2" s="139"/>
-      <c r="CS2" s="131"/>
-      <c r="CT2" s="132"/>
-      <c r="CU2" s="132"/>
-      <c r="CV2" s="132"/>
-      <c r="CW2" s="133"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="171"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="165"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="142"/>
+      <c r="X2" s="166"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="123"/>
+      <c r="AB2" s="141"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
+      <c r="AH2" s="123"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="142"/>
+      <c r="AL2" s="166"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="123"/>
+      <c r="AO2" s="123"/>
+      <c r="AP2" s="123"/>
+      <c r="AQ2" s="123"/>
+      <c r="AR2" s="123"/>
+      <c r="AS2" s="123"/>
+      <c r="AT2" s="123"/>
+      <c r="AU2" s="165"/>
+      <c r="AV2" s="123"/>
+      <c r="AW2" s="123"/>
+      <c r="AX2" s="123"/>
+      <c r="AY2" s="123"/>
+      <c r="AZ2" s="123"/>
+      <c r="BA2" s="123"/>
+      <c r="BB2" s="123"/>
+      <c r="BC2" s="123"/>
+      <c r="BD2" s="123"/>
+      <c r="BE2" s="123"/>
+      <c r="BF2" s="123"/>
+      <c r="BG2" s="123"/>
+      <c r="BH2" s="123"/>
+      <c r="BI2" s="123"/>
+      <c r="BJ2" s="123"/>
+      <c r="BK2" s="123"/>
+      <c r="BL2" s="123"/>
+      <c r="BM2" s="123"/>
+      <c r="BN2" s="123"/>
+      <c r="BO2" s="123"/>
+      <c r="BP2" s="123"/>
+      <c r="BQ2" s="123"/>
+      <c r="BR2" s="123"/>
+      <c r="BS2" s="123"/>
+      <c r="BT2" s="123"/>
+      <c r="BU2" s="123"/>
+      <c r="BV2" s="199"/>
+      <c r="BW2" s="123"/>
+      <c r="BX2" s="123"/>
+      <c r="BY2" s="123"/>
+      <c r="BZ2" s="123"/>
+      <c r="CA2" s="123"/>
+      <c r="CB2" s="123"/>
+      <c r="CC2" s="123"/>
+      <c r="CD2" s="123"/>
+      <c r="CE2" s="123"/>
+      <c r="CF2" s="123"/>
+      <c r="CG2" s="123"/>
+      <c r="CH2" s="123"/>
+      <c r="CI2" s="123"/>
+      <c r="CJ2" s="123"/>
+      <c r="CK2" s="123"/>
+      <c r="CL2" s="123"/>
+      <c r="CM2" s="123"/>
+      <c r="CN2" s="123"/>
+      <c r="CO2" s="123"/>
+      <c r="CP2" s="123"/>
+      <c r="CQ2" s="123"/>
+      <c r="CR2" s="142"/>
+      <c r="CS2" s="197"/>
+      <c r="CT2" s="185"/>
+      <c r="CU2" s="185"/>
+      <c r="CV2" s="185"/>
+      <c r="CW2" s="198"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="146">
+      <c r="CY2" s="186">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>35</v>
       </c>
@@ -5009,113 +5025,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="178" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="127"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="185" t="s">
+      <c r="E3" s="123"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="179"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="127"/>
-      <c r="V3" s="127"/>
-      <c r="W3" s="139"/>
-      <c r="X3" s="169"/>
-      <c r="Y3" s="127"/>
-      <c r="Z3" s="127"/>
-      <c r="AA3" s="127"/>
-      <c r="AB3" s="168"/>
-      <c r="AC3" s="127"/>
-      <c r="AD3" s="127"/>
-      <c r="AE3" s="127"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="127"/>
-      <c r="AH3" s="127"/>
-      <c r="AI3" s="127"/>
-      <c r="AJ3" s="127"/>
-      <c r="AK3" s="139"/>
-      <c r="AL3" s="126"/>
-      <c r="AM3" s="127"/>
-      <c r="AN3" s="127"/>
-      <c r="AO3" s="127"/>
-      <c r="AP3" s="127"/>
-      <c r="AQ3" s="127"/>
-      <c r="AR3" s="127"/>
-      <c r="AS3" s="127"/>
-      <c r="AT3" s="127"/>
-      <c r="AU3" s="152"/>
-      <c r="AV3" s="127"/>
-      <c r="AW3" s="127"/>
-      <c r="AX3" s="127"/>
-      <c r="AY3" s="127"/>
-      <c r="AZ3" s="127"/>
-      <c r="BA3" s="127"/>
-      <c r="BB3" s="127"/>
-      <c r="BC3" s="127"/>
-      <c r="BD3" s="127"/>
-      <c r="BE3" s="127"/>
-      <c r="BF3" s="127"/>
-      <c r="BG3" s="127"/>
-      <c r="BH3" s="127"/>
-      <c r="BI3" s="127"/>
-      <c r="BJ3" s="127"/>
-      <c r="BK3" s="127"/>
-      <c r="BL3" s="127"/>
-      <c r="BM3" s="127"/>
-      <c r="BN3" s="127"/>
-      <c r="BO3" s="127"/>
-      <c r="BP3" s="127"/>
-      <c r="BQ3" s="127"/>
-      <c r="BR3" s="127"/>
-      <c r="BS3" s="127"/>
-      <c r="BT3" s="127"/>
-      <c r="BU3" s="127"/>
-      <c r="BV3" s="140"/>
-      <c r="BW3" s="127"/>
-      <c r="BX3" s="127"/>
-      <c r="BY3" s="127"/>
-      <c r="BZ3" s="127"/>
-      <c r="CA3" s="127"/>
-      <c r="CB3" s="127"/>
-      <c r="CC3" s="127"/>
-      <c r="CD3" s="127"/>
-      <c r="CE3" s="127"/>
-      <c r="CF3" s="127"/>
-      <c r="CG3" s="127"/>
-      <c r="CH3" s="127"/>
-      <c r="CI3" s="127"/>
-      <c r="CJ3" s="127"/>
-      <c r="CK3" s="127"/>
-      <c r="CL3" s="127"/>
-      <c r="CM3" s="127"/>
-      <c r="CN3" s="127"/>
-      <c r="CO3" s="127"/>
-      <c r="CP3" s="127"/>
-      <c r="CQ3" s="127"/>
-      <c r="CR3" s="139"/>
-      <c r="CS3" s="131"/>
-      <c r="CT3" s="132"/>
-      <c r="CU3" s="132"/>
-      <c r="CV3" s="132"/>
-      <c r="CW3" s="133"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="142"/>
+      <c r="X3" s="167"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="123"/>
+      <c r="AB3" s="157"/>
+      <c r="AC3" s="123"/>
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
+      <c r="AF3" s="123"/>
+      <c r="AG3" s="123"/>
+      <c r="AH3" s="123"/>
+      <c r="AI3" s="123"/>
+      <c r="AJ3" s="123"/>
+      <c r="AK3" s="142"/>
+      <c r="AL3" s="193"/>
+      <c r="AM3" s="123"/>
+      <c r="AN3" s="123"/>
+      <c r="AO3" s="123"/>
+      <c r="AP3" s="123"/>
+      <c r="AQ3" s="123"/>
+      <c r="AR3" s="123"/>
+      <c r="AS3" s="123"/>
+      <c r="AT3" s="123"/>
+      <c r="AU3" s="187"/>
+      <c r="AV3" s="123"/>
+      <c r="AW3" s="123"/>
+      <c r="AX3" s="123"/>
+      <c r="AY3" s="123"/>
+      <c r="AZ3" s="123"/>
+      <c r="BA3" s="123"/>
+      <c r="BB3" s="123"/>
+      <c r="BC3" s="123"/>
+      <c r="BD3" s="123"/>
+      <c r="BE3" s="123"/>
+      <c r="BF3" s="123"/>
+      <c r="BG3" s="123"/>
+      <c r="BH3" s="123"/>
+      <c r="BI3" s="123"/>
+      <c r="BJ3" s="123"/>
+      <c r="BK3" s="123"/>
+      <c r="BL3" s="123"/>
+      <c r="BM3" s="123"/>
+      <c r="BN3" s="123"/>
+      <c r="BO3" s="123"/>
+      <c r="BP3" s="123"/>
+      <c r="BQ3" s="123"/>
+      <c r="BR3" s="123"/>
+      <c r="BS3" s="123"/>
+      <c r="BT3" s="123"/>
+      <c r="BU3" s="123"/>
+      <c r="BV3" s="200"/>
+      <c r="BW3" s="123"/>
+      <c r="BX3" s="123"/>
+      <c r="BY3" s="123"/>
+      <c r="BZ3" s="123"/>
+      <c r="CA3" s="123"/>
+      <c r="CB3" s="123"/>
+      <c r="CC3" s="123"/>
+      <c r="CD3" s="123"/>
+      <c r="CE3" s="123"/>
+      <c r="CF3" s="123"/>
+      <c r="CG3" s="123"/>
+      <c r="CH3" s="123"/>
+      <c r="CI3" s="123"/>
+      <c r="CJ3" s="123"/>
+      <c r="CK3" s="123"/>
+      <c r="CL3" s="123"/>
+      <c r="CM3" s="123"/>
+      <c r="CN3" s="123"/>
+      <c r="CO3" s="123"/>
+      <c r="CP3" s="123"/>
+      <c r="CQ3" s="123"/>
+      <c r="CR3" s="142"/>
+      <c r="CS3" s="197"/>
+      <c r="CT3" s="185"/>
+      <c r="CU3" s="185"/>
+      <c r="CV3" s="185"/>
+      <c r="CW3" s="198"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -5144,142 +5160,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="177"/>
-      <c r="D4" s="184" t="s">
+      <c r="B4" s="123"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="127"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="186" t="s">
+      <c r="E4" s="123"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="143"/>
-      <c r="O4" s="143"/>
-      <c r="P4" s="188"/>
-      <c r="Q4" s="143"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="143"/>
-      <c r="T4" s="189"/>
-      <c r="U4" s="143"/>
-      <c r="V4" s="143"/>
-      <c r="W4" s="144"/>
-      <c r="X4" s="190"/>
-      <c r="Y4" s="143"/>
-      <c r="Z4" s="143"/>
-      <c r="AA4" s="143"/>
-      <c r="AB4" s="191"/>
-      <c r="AC4" s="143"/>
-      <c r="AD4" s="143"/>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="144"/>
-      <c r="AL4" s="142"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="143"/>
-      <c r="AQ4" s="143"/>
-      <c r="AR4" s="143"/>
-      <c r="AS4" s="143"/>
-      <c r="AT4" s="144"/>
-      <c r="AU4" s="153"/>
-      <c r="AV4" s="143"/>
-      <c r="AW4" s="143"/>
-      <c r="AX4" s="143"/>
-      <c r="AY4" s="143"/>
-      <c r="AZ4" s="143"/>
-      <c r="BA4" s="143"/>
-      <c r="BB4" s="143"/>
-      <c r="BC4" s="143"/>
-      <c r="BD4" s="143"/>
-      <c r="BE4" s="143"/>
-      <c r="BF4" s="143"/>
-      <c r="BG4" s="143"/>
-      <c r="BH4" s="143"/>
-      <c r="BI4" s="143"/>
-      <c r="BJ4" s="143"/>
-      <c r="BK4" s="143"/>
-      <c r="BL4" s="143"/>
-      <c r="BM4" s="143"/>
-      <c r="BN4" s="143"/>
-      <c r="BO4" s="143"/>
-      <c r="BP4" s="143"/>
-      <c r="BQ4" s="143"/>
-      <c r="BR4" s="143"/>
-      <c r="BS4" s="143"/>
-      <c r="BT4" s="143"/>
-      <c r="BU4" s="143"/>
-      <c r="BV4" s="154"/>
-      <c r="BW4" s="143"/>
-      <c r="BX4" s="143"/>
-      <c r="BY4" s="143"/>
-      <c r="BZ4" s="143"/>
-      <c r="CA4" s="143"/>
-      <c r="CB4" s="143"/>
-      <c r="CC4" s="143"/>
-      <c r="CD4" s="143"/>
-      <c r="CE4" s="143"/>
-      <c r="CF4" s="143"/>
-      <c r="CG4" s="143"/>
-      <c r="CH4" s="143"/>
-      <c r="CI4" s="143"/>
-      <c r="CJ4" s="143"/>
-      <c r="CK4" s="143"/>
-      <c r="CL4" s="143"/>
-      <c r="CM4" s="143"/>
-      <c r="CN4" s="143"/>
-      <c r="CO4" s="143"/>
-      <c r="CP4" s="143"/>
-      <c r="CQ4" s="143"/>
-      <c r="CR4" s="144"/>
-      <c r="CS4" s="131"/>
-      <c r="CT4" s="132"/>
-      <c r="CU4" s="132"/>
-      <c r="CV4" s="132"/>
-      <c r="CW4" s="133"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="148"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
+      <c r="S4" s="126"/>
+      <c r="T4" s="151"/>
+      <c r="U4" s="126"/>
+      <c r="V4" s="126"/>
+      <c r="W4" s="152"/>
+      <c r="X4" s="154"/>
+      <c r="Y4" s="126"/>
+      <c r="Z4" s="126"/>
+      <c r="AA4" s="126"/>
+      <c r="AB4" s="155"/>
+      <c r="AC4" s="126"/>
+      <c r="AD4" s="126"/>
+      <c r="AE4" s="126"/>
+      <c r="AF4" s="126"/>
+      <c r="AG4" s="126"/>
+      <c r="AH4" s="126"/>
+      <c r="AI4" s="126"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="152"/>
+      <c r="AL4" s="201"/>
+      <c r="AM4" s="126"/>
+      <c r="AN4" s="126"/>
+      <c r="AO4" s="126"/>
+      <c r="AP4" s="126"/>
+      <c r="AQ4" s="126"/>
+      <c r="AR4" s="126"/>
+      <c r="AS4" s="126"/>
+      <c r="AT4" s="152"/>
+      <c r="AU4" s="188"/>
+      <c r="AV4" s="126"/>
+      <c r="AW4" s="126"/>
+      <c r="AX4" s="126"/>
+      <c r="AY4" s="126"/>
+      <c r="AZ4" s="126"/>
+      <c r="BA4" s="126"/>
+      <c r="BB4" s="126"/>
+      <c r="BC4" s="126"/>
+      <c r="BD4" s="126"/>
+      <c r="BE4" s="126"/>
+      <c r="BF4" s="126"/>
+      <c r="BG4" s="126"/>
+      <c r="BH4" s="126"/>
+      <c r="BI4" s="126"/>
+      <c r="BJ4" s="126"/>
+      <c r="BK4" s="126"/>
+      <c r="BL4" s="126"/>
+      <c r="BM4" s="126"/>
+      <c r="BN4" s="126"/>
+      <c r="BO4" s="126"/>
+      <c r="BP4" s="126"/>
+      <c r="BQ4" s="126"/>
+      <c r="BR4" s="126"/>
+      <c r="BS4" s="126"/>
+      <c r="BT4" s="126"/>
+      <c r="BU4" s="126"/>
+      <c r="BV4" s="189"/>
+      <c r="BW4" s="126"/>
+      <c r="BX4" s="126"/>
+      <c r="BY4" s="126"/>
+      <c r="BZ4" s="126"/>
+      <c r="CA4" s="126"/>
+      <c r="CB4" s="126"/>
+      <c r="CC4" s="126"/>
+      <c r="CD4" s="126"/>
+      <c r="CE4" s="126"/>
+      <c r="CF4" s="126"/>
+      <c r="CG4" s="126"/>
+      <c r="CH4" s="126"/>
+      <c r="CI4" s="126"/>
+      <c r="CJ4" s="126"/>
+      <c r="CK4" s="126"/>
+      <c r="CL4" s="126"/>
+      <c r="CM4" s="126"/>
+      <c r="CN4" s="126"/>
+      <c r="CO4" s="126"/>
+      <c r="CP4" s="126"/>
+      <c r="CQ4" s="126"/>
+      <c r="CR4" s="152"/>
+      <c r="CS4" s="197"/>
+      <c r="CT4" s="185"/>
+      <c r="CU4" s="185"/>
+      <c r="CV4" s="185"/>
+      <c r="CW4" s="198"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="148" t="s">
+      <c r="CY4" s="175" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="149"/>
-      <c r="DA4" s="150" t="s">
+      <c r="CZ4" s="176"/>
+      <c r="DA4" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="151"/>
-      <c r="DC4" s="151"/>
-      <c r="DD4" s="151"/>
-      <c r="DE4" s="151"/>
-      <c r="DF4" s="151"/>
-      <c r="DG4" s="149"/>
+      <c r="DB4" s="178"/>
+      <c r="DC4" s="178"/>
+      <c r="DD4" s="178"/>
+      <c r="DE4" s="178"/>
+      <c r="DF4" s="178"/>
+      <c r="DG4" s="176"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="148" t="s">
+      <c r="DJ4" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="149"/>
-      <c r="DL4" s="150" t="s">
+      <c r="DK4" s="176"/>
+      <c r="DL4" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="151"/>
-      <c r="DN4" s="151"/>
-      <c r="DO4" s="151"/>
-      <c r="DP4" s="151"/>
-      <c r="DQ4" s="151"/>
-      <c r="DR4" s="149"/>
+      <c r="DM4" s="178"/>
+      <c r="DN4" s="178"/>
+      <c r="DO4" s="178"/>
+      <c r="DP4" s="178"/>
+      <c r="DQ4" s="178"/>
+      <c r="DR4" s="176"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5287,18 +5303,18 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="177"/>
-      <c r="D5" s="192" t="str">
+      <c r="B5" s="123"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="156" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO GENERAL SANTADER</v>
       </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="187"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="146"/>
       <c r="H5" s="147"/>
       <c r="I5" s="147"/>
       <c r="J5" s="147"/>
@@ -5307,92 +5323,92 @@
       <c r="M5" s="147"/>
       <c r="N5" s="147"/>
       <c r="O5" s="147"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="135"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="136"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="135"/>
-      <c r="Z5" s="135"/>
-      <c r="AA5" s="135"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="135"/>
-      <c r="AD5" s="135"/>
-      <c r="AE5" s="135"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="136"/>
-      <c r="AL5" s="134"/>
-      <c r="AM5" s="135"/>
-      <c r="AN5" s="135"/>
-      <c r="AO5" s="135"/>
-      <c r="AP5" s="135"/>
-      <c r="AQ5" s="135"/>
-      <c r="AR5" s="135"/>
-      <c r="AS5" s="135"/>
-      <c r="AT5" s="136"/>
-      <c r="AU5" s="134"/>
-      <c r="AV5" s="135"/>
-      <c r="AW5" s="135"/>
-      <c r="AX5" s="135"/>
-      <c r="AY5" s="135"/>
-      <c r="AZ5" s="135"/>
-      <c r="BA5" s="135"/>
-      <c r="BB5" s="135"/>
-      <c r="BC5" s="135"/>
-      <c r="BD5" s="135"/>
-      <c r="BE5" s="135"/>
-      <c r="BF5" s="135"/>
-      <c r="BG5" s="135"/>
-      <c r="BH5" s="135"/>
-      <c r="BI5" s="135"/>
-      <c r="BJ5" s="135"/>
-      <c r="BK5" s="135"/>
-      <c r="BL5" s="135"/>
-      <c r="BM5" s="135"/>
-      <c r="BN5" s="135"/>
-      <c r="BO5" s="135"/>
-      <c r="BP5" s="135"/>
-      <c r="BQ5" s="135"/>
-      <c r="BR5" s="135"/>
-      <c r="BS5" s="135"/>
-      <c r="BT5" s="135"/>
-      <c r="BU5" s="135"/>
-      <c r="BV5" s="134"/>
-      <c r="BW5" s="135"/>
-      <c r="BX5" s="135"/>
-      <c r="BY5" s="135"/>
-      <c r="BZ5" s="135"/>
-      <c r="CA5" s="135"/>
-      <c r="CB5" s="135"/>
-      <c r="CC5" s="135"/>
-      <c r="CD5" s="135"/>
-      <c r="CE5" s="135"/>
-      <c r="CF5" s="135"/>
-      <c r="CG5" s="135"/>
-      <c r="CH5" s="135"/>
-      <c r="CI5" s="135"/>
-      <c r="CJ5" s="135"/>
-      <c r="CK5" s="135"/>
-      <c r="CL5" s="135"/>
-      <c r="CM5" s="135"/>
-      <c r="CN5" s="135"/>
-      <c r="CO5" s="135"/>
-      <c r="CP5" s="135"/>
-      <c r="CQ5" s="135"/>
-      <c r="CR5" s="136"/>
-      <c r="CS5" s="134"/>
-      <c r="CT5" s="135"/>
-      <c r="CU5" s="135"/>
-      <c r="CV5" s="135"/>
-      <c r="CW5" s="136"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="150"/>
+      <c r="R5" s="150"/>
+      <c r="S5" s="150"/>
+      <c r="T5" s="149"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="150"/>
+      <c r="W5" s="153"/>
+      <c r="X5" s="149"/>
+      <c r="Y5" s="150"/>
+      <c r="Z5" s="150"/>
+      <c r="AA5" s="150"/>
+      <c r="AB5" s="149"/>
+      <c r="AC5" s="150"/>
+      <c r="AD5" s="150"/>
+      <c r="AE5" s="150"/>
+      <c r="AF5" s="150"/>
+      <c r="AG5" s="150"/>
+      <c r="AH5" s="150"/>
+      <c r="AI5" s="150"/>
+      <c r="AJ5" s="150"/>
+      <c r="AK5" s="153"/>
+      <c r="AL5" s="149"/>
+      <c r="AM5" s="150"/>
+      <c r="AN5" s="150"/>
+      <c r="AO5" s="150"/>
+      <c r="AP5" s="150"/>
+      <c r="AQ5" s="150"/>
+      <c r="AR5" s="150"/>
+      <c r="AS5" s="150"/>
+      <c r="AT5" s="153"/>
+      <c r="AU5" s="149"/>
+      <c r="AV5" s="150"/>
+      <c r="AW5" s="150"/>
+      <c r="AX5" s="150"/>
+      <c r="AY5" s="150"/>
+      <c r="AZ5" s="150"/>
+      <c r="BA5" s="150"/>
+      <c r="BB5" s="150"/>
+      <c r="BC5" s="150"/>
+      <c r="BD5" s="150"/>
+      <c r="BE5" s="150"/>
+      <c r="BF5" s="150"/>
+      <c r="BG5" s="150"/>
+      <c r="BH5" s="150"/>
+      <c r="BI5" s="150"/>
+      <c r="BJ5" s="150"/>
+      <c r="BK5" s="150"/>
+      <c r="BL5" s="150"/>
+      <c r="BM5" s="150"/>
+      <c r="BN5" s="150"/>
+      <c r="BO5" s="150"/>
+      <c r="BP5" s="150"/>
+      <c r="BQ5" s="150"/>
+      <c r="BR5" s="150"/>
+      <c r="BS5" s="150"/>
+      <c r="BT5" s="150"/>
+      <c r="BU5" s="150"/>
+      <c r="BV5" s="149"/>
+      <c r="BW5" s="150"/>
+      <c r="BX5" s="150"/>
+      <c r="BY5" s="150"/>
+      <c r="BZ5" s="150"/>
+      <c r="CA5" s="150"/>
+      <c r="CB5" s="150"/>
+      <c r="CC5" s="150"/>
+      <c r="CD5" s="150"/>
+      <c r="CE5" s="150"/>
+      <c r="CF5" s="150"/>
+      <c r="CG5" s="150"/>
+      <c r="CH5" s="150"/>
+      <c r="CI5" s="150"/>
+      <c r="CJ5" s="150"/>
+      <c r="CK5" s="150"/>
+      <c r="CL5" s="150"/>
+      <c r="CM5" s="150"/>
+      <c r="CN5" s="150"/>
+      <c r="CO5" s="150"/>
+      <c r="CP5" s="150"/>
+      <c r="CQ5" s="150"/>
+      <c r="CR5" s="153"/>
+      <c r="CS5" s="149"/>
+      <c r="CT5" s="150"/>
+      <c r="CU5" s="150"/>
+      <c r="CV5" s="150"/>
+      <c r="CW5" s="153"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5421,11 +5437,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="176" t="s">
+      <c r="A6" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="127"/>
-      <c r="C6" s="177"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="124"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3414937</v>
@@ -5437,18 +5453,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="198" t="str">
+      <c r="G6" s="125" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 35</v>
       </c>
-      <c r="H6" s="143"/>
-      <c r="I6" s="143"/>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="143"/>
-      <c r="M6" s="143"/>
-      <c r="N6" s="143"/>
-      <c r="O6" s="194"/>
+      <c r="H6" s="126"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="126"/>
+      <c r="O6" s="127"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5793,41 +5809,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="155" t="s">
+      <c r="CX6" s="179" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="156"/>
-      <c r="CZ6" s="156"/>
-      <c r="DA6" s="156"/>
-      <c r="DB6" s="156"/>
-      <c r="DC6" s="156"/>
-      <c r="DD6" s="156"/>
-      <c r="DE6" s="156"/>
-      <c r="DF6" s="156"/>
-      <c r="DG6" s="156"/>
-      <c r="DH6" s="156"/>
-      <c r="DI6" s="156"/>
-      <c r="DJ6" s="156"/>
-      <c r="DK6" s="156"/>
-      <c r="DL6" s="156"/>
-      <c r="DM6" s="156"/>
-      <c r="DN6" s="156"/>
-      <c r="DO6" s="156"/>
-      <c r="DP6" s="156"/>
-      <c r="DQ6" s="156"/>
-      <c r="DR6" s="156"/>
-      <c r="DS6" s="156"/>
-      <c r="DT6" s="156"/>
-      <c r="DU6" s="156"/>
-      <c r="DV6" s="156"/>
-      <c r="DW6" s="156"/>
+      <c r="CY6" s="180"/>
+      <c r="CZ6" s="180"/>
+      <c r="DA6" s="180"/>
+      <c r="DB6" s="180"/>
+      <c r="DC6" s="180"/>
+      <c r="DD6" s="180"/>
+      <c r="DE6" s="180"/>
+      <c r="DF6" s="180"/>
+      <c r="DG6" s="180"/>
+      <c r="DH6" s="180"/>
+      <c r="DI6" s="180"/>
+      <c r="DJ6" s="180"/>
+      <c r="DK6" s="180"/>
+      <c r="DL6" s="180"/>
+      <c r="DM6" s="180"/>
+      <c r="DN6" s="180"/>
+      <c r="DO6" s="180"/>
+      <c r="DP6" s="180"/>
+      <c r="DQ6" s="180"/>
+      <c r="DR6" s="180"/>
+      <c r="DS6" s="180"/>
+      <c r="DT6" s="180"/>
+      <c r="DU6" s="180"/>
+      <c r="DV6" s="180"/>
+      <c r="DW6" s="180"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="199" t="s">
+      <c r="A7" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="177"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="124"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46084</v>
@@ -5839,15 +5855,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46086</v>
       </c>
-      <c r="G7" s="195"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
-      <c r="J7" s="175"/>
-      <c r="K7" s="175"/>
-      <c r="L7" s="175"/>
-      <c r="M7" s="175"/>
-      <c r="N7" s="175"/>
-      <c r="O7" s="196"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="130"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46084</v>
@@ -6192,58 +6208,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46380</v>
       </c>
-      <c r="CX7" s="157" t="s">
+      <c r="CX7" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="158"/>
-      <c r="CZ7" s="157" t="s">
+      <c r="CY7" s="182"/>
+      <c r="CZ7" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="156"/>
-      <c r="DB7" s="157" t="s">
+      <c r="DA7" s="180"/>
+      <c r="DB7" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="158"/>
-      <c r="DD7" s="157" t="s">
+      <c r="DC7" s="182"/>
+      <c r="DD7" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="158"/>
-      <c r="DF7" s="157" t="s">
+      <c r="DE7" s="182"/>
+      <c r="DF7" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="158"/>
-      <c r="DH7" s="157" t="s">
+      <c r="DG7" s="182"/>
+      <c r="DH7" s="181" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="158"/>
-      <c r="DJ7" s="157" t="s">
+      <c r="DI7" s="182"/>
+      <c r="DJ7" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="158"/>
-      <c r="DL7" s="157" t="s">
+      <c r="DK7" s="182"/>
+      <c r="DL7" s="181" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="158"/>
-      <c r="DN7" s="157" t="s">
+      <c r="DM7" s="182"/>
+      <c r="DN7" s="181" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="158"/>
-      <c r="DP7" s="157" t="s">
+      <c r="DO7" s="182"/>
+      <c r="DP7" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="158"/>
-      <c r="DR7" s="157" t="s">
+      <c r="DQ7" s="182"/>
+      <c r="DR7" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="158"/>
-      <c r="DT7" s="157" t="s">
+      <c r="DS7" s="182"/>
+      <c r="DT7" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="158"/>
-      <c r="DV7" s="159" t="s">
+      <c r="DU7" s="182"/>
+      <c r="DV7" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="156"/>
+      <c r="DW7" s="180"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -6742,7 +6758,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G13" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H13" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -6802,7 +6818,9 @@
       </c>
       <c r="X9" s="35"/>
       <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
+      <c r="Z9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA9" s="35"/>
       <c r="AB9" s="35"/>
       <c r="AC9" s="35"/>
@@ -6940,7 +6958,7 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="4"/>
@@ -6972,7 +6990,7 @@
       </c>
       <c r="O10" s="34">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P10" s="35" t="s">
         <v>11</v>
@@ -7000,7 +7018,9 @@
       </c>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
+      <c r="Z10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -7138,7 +7158,7 @@
       </c>
       <c r="G11" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" si="4"/>
@@ -7198,7 +7218,9 @@
       </c>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
+      <c r="Z11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA11" s="35"/>
       <c r="AB11" s="35"/>
       <c r="AC11" s="35"/>
@@ -7332,7 +7354,7 @@
       </c>
       <c r="F12" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G12" s="41">
         <f t="shared" si="3"/>
@@ -7344,7 +7366,7 @@
       </c>
       <c r="I12" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="6"/>
@@ -7368,7 +7390,7 @@
       </c>
       <c r="O12" s="34">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P12" s="35" t="s">
         <v>38</v>
@@ -7396,7 +7418,9 @@
       </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
+      <c r="Z12" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA12" s="35"/>
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
@@ -7534,7 +7558,7 @@
       </c>
       <c r="G13" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" si="4"/>
@@ -7594,7 +7618,9 @@
       </c>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
+      <c r="Z13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA13" s="35"/>
       <c r="AB13" s="35"/>
       <c r="AC13" s="35"/>
@@ -7732,7 +7758,7 @@
       </c>
       <c r="G14" s="41">
         <f t="shared" ref="G14" si="18">COUNTIF(P14:CR14,"A")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="42">
         <f t="shared" ref="H14" si="19">COUNTIF(P14:CR14,"CE")</f>
@@ -7764,7 +7790,7 @@
       </c>
       <c r="O14" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P14" s="35" t="s">
         <v>38</v>
@@ -7792,7 +7818,9 @@
       </c>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
+      <c r="Z14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA14" s="35"/>
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
@@ -7930,7 +7958,7 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" ref="G15:G43" si="27">COUNTIF(P14:CR14,"A")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="42">
         <f t="shared" ref="H15:I43" si="28">COUNTIF(P14:CR14,"CE")</f>
@@ -7962,7 +7990,7 @@
       </c>
       <c r="O15" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P15" s="35" t="s">
         <v>38</v>
@@ -7990,7 +8018,9 @@
       </c>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
+      <c r="Z15" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA15" s="35"/>
       <c r="AB15" s="35"/>
       <c r="AC15" s="35"/>
@@ -8188,7 +8218,9 @@
       </c>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
+      <c r="Z16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA16" s="35"/>
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
@@ -8326,7 +8358,7 @@
       </c>
       <c r="G17" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="42">
         <f t="shared" si="28"/>
@@ -8358,7 +8390,7 @@
       </c>
       <c r="O17" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P17" s="35" t="s">
         <v>38</v>
@@ -8386,7 +8418,9 @@
       </c>
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="Z17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA17" s="35"/>
       <c r="AB17" s="35"/>
       <c r="AC17" s="35"/>
@@ -8524,7 +8558,7 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="28"/>
@@ -8556,7 +8590,7 @@
       </c>
       <c r="O18" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P18" s="35" t="s">
         <v>38</v>
@@ -8584,7 +8618,9 @@
       </c>
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="Z18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA18" s="35"/>
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
@@ -8722,7 +8758,7 @@
       </c>
       <c r="G19" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" s="42">
         <f t="shared" si="28"/>
@@ -8782,7 +8818,9 @@
       </c>
       <c r="X19" s="35"/>
       <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="Z19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA19" s="35"/>
       <c r="AB19" s="35"/>
       <c r="AC19" s="35"/>
@@ -8920,7 +8958,7 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="28"/>
@@ -8980,7 +9018,9 @@
       </c>
       <c r="X20" s="35"/>
       <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="Z20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA20" s="35"/>
       <c r="AB20" s="35"/>
       <c r="AC20" s="35"/>
@@ -9118,7 +9158,7 @@
       </c>
       <c r="G21" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="28"/>
@@ -9178,7 +9218,9 @@
       </c>
       <c r="X21" s="35"/>
       <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="Z21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA21" s="35"/>
       <c r="AB21" s="35"/>
       <c r="AC21" s="35"/>
@@ -9314,7 +9356,7 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="28"/>
@@ -9374,7 +9416,9 @@
       </c>
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="Z22" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA22" s="35"/>
       <c r="AB22" s="35"/>
       <c r="AC22" s="35"/>
@@ -9506,7 +9550,7 @@
       </c>
       <c r="F23" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G23" s="41">
         <f t="shared" si="27"/>
@@ -9518,7 +9562,7 @@
       </c>
       <c r="I23" s="42">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="42">
         <f t="shared" si="30"/>
@@ -9542,7 +9586,7 @@
       </c>
       <c r="O23" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P23" s="35" t="s">
         <v>38</v>
@@ -9570,7 +9614,9 @@
       </c>
       <c r="X23" s="35"/>
       <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="Z23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA23" s="35"/>
       <c r="AB23" s="35"/>
       <c r="AC23" s="35"/>
@@ -9681,19 +9727,19 @@
       <c r="DY23" s="39"/>
     </row>
     <row r="24" spans="1:129" ht="15.75" customHeight="1">
-      <c r="A24" s="40">
+      <c r="A24" s="215">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="B24" s="26" t="str">
+      <c r="B24" s="216" t="str">
         <f>'BASE DE DATOS'!C25</f>
         <v>TI</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="217">
         <f>'BASE DE DATOS'!D25</f>
         <v>1087819083</v>
       </c>
-      <c r="D24" s="28" t="str">
+      <c r="D24" s="218" t="str">
         <f>'BASE DE DATOS'!B25</f>
         <v>Sharith Yesid González Rodríguez</v>
       </c>
@@ -9706,7 +9752,7 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="28"/>
@@ -9766,7 +9812,9 @@
       </c>
       <c r="X24" s="35"/>
       <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="Z24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA24" s="35"/>
       <c r="AB24" s="35"/>
       <c r="AC24" s="35"/>
@@ -9902,7 +9950,7 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="42">
         <f t="shared" si="28"/>
@@ -9962,7 +10010,9 @@
       </c>
       <c r="X25" s="35"/>
       <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="Z25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA25" s="35"/>
       <c r="AB25" s="35"/>
       <c r="AC25" s="35"/>
@@ -10098,7 +10148,7 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="28"/>
@@ -10158,7 +10208,9 @@
       </c>
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="Z26" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA26" s="35"/>
       <c r="AB26" s="35"/>
       <c r="AC26" s="35"/>
@@ -10290,7 +10342,7 @@
       </c>
       <c r="F27" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G27" s="41">
         <f t="shared" si="27"/>
@@ -10302,7 +10354,7 @@
       </c>
       <c r="I27" s="42">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="42">
         <f t="shared" si="30"/>
@@ -10326,7 +10378,7 @@
       </c>
       <c r="O27" s="34">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P27" s="35" t="s">
         <v>38</v>
@@ -10354,7 +10406,9 @@
       </c>
       <c r="X27" s="35"/>
       <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="Z27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA27" s="35"/>
       <c r="AB27" s="35"/>
       <c r="AC27" s="35"/>
@@ -10490,7 +10544,7 @@
       </c>
       <c r="G28" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="28"/>
@@ -10550,7 +10604,9 @@
       </c>
       <c r="X28" s="35"/>
       <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="Z28" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA28" s="35"/>
       <c r="AB28" s="35"/>
       <c r="AC28" s="35"/>
@@ -10694,7 +10750,7 @@
       </c>
       <c r="I29" s="42">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="42">
         <f t="shared" si="30"/>
@@ -10718,7 +10774,7 @@
       </c>
       <c r="O29" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P29" s="35" t="s">
         <v>38</v>
@@ -10746,7 +10802,9 @@
       </c>
       <c r="X29" s="35"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="Z29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA29" s="35"/>
       <c r="AB29" s="35"/>
       <c r="AC29" s="35"/>
@@ -10882,7 +10940,7 @@
       </c>
       <c r="G30" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" s="42">
         <f t="shared" si="28"/>
@@ -10914,7 +10972,7 @@
       </c>
       <c r="O30" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P30" s="35" t="s">
         <v>38</v>
@@ -10942,7 +11000,9 @@
       </c>
       <c r="X30" s="35"/>
       <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="Z30" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA30" s="35"/>
       <c r="AB30" s="35"/>
       <c r="AC30" s="35"/>
@@ -11078,7 +11138,7 @@
       </c>
       <c r="G31" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" s="42">
         <f t="shared" si="28"/>
@@ -11138,7 +11198,9 @@
       </c>
       <c r="X31" s="35"/>
       <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="Z31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA31" s="35"/>
       <c r="AB31" s="35"/>
       <c r="AC31" s="35"/>
@@ -11273,7 +11335,7 @@
       </c>
       <c r="G32" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="28"/>
@@ -11305,7 +11367,7 @@
       </c>
       <c r="O32" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P32" s="35" t="s">
         <v>38</v>
@@ -11333,7 +11395,9 @@
       </c>
       <c r="X32" s="35"/>
       <c r="Y32" s="35"/>
-      <c r="Z32" s="35"/>
+      <c r="Z32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA32" s="35"/>
       <c r="AB32" s="35"/>
       <c r="AC32" s="35"/>
@@ -11468,7 +11532,7 @@
       </c>
       <c r="G33" s="41">
         <f t="shared" si="27"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H33" s="42">
         <f t="shared" si="28"/>
@@ -11500,7 +11564,7 @@
       </c>
       <c r="O33" s="34">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P33" s="35" t="s">
         <v>38</v>
@@ -11528,7 +11592,9 @@
       </c>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
-      <c r="Z33" s="35"/>
+      <c r="Z33" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA33" s="35"/>
       <c r="AB33" s="35"/>
       <c r="AC33" s="35"/>
@@ -11663,7 +11729,7 @@
       </c>
       <c r="G34" s="41">
         <f t="shared" ref="G34" si="54">COUNTIF(P33:CR33,"A")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34" s="42">
         <f t="shared" ref="H34" si="55">COUNTIF(P33:CR33,"CE")</f>
@@ -11723,7 +11789,9 @@
       </c>
       <c r="X34" s="35"/>
       <c r="Y34" s="35"/>
-      <c r="Z34" s="35"/>
+      <c r="Z34" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA34" s="35"/>
       <c r="AB34" s="35"/>
       <c r="AC34" s="35"/>
@@ -11858,7 +11926,7 @@
       </c>
       <c r="G35" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H35" s="42">
         <f t="shared" si="28"/>
@@ -11890,7 +11958,7 @@
       </c>
       <c r="O35" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P35" s="35" t="s">
         <v>38</v>
@@ -11918,7 +11986,9 @@
       </c>
       <c r="X35" s="35"/>
       <c r="Y35" s="35"/>
-      <c r="Z35" s="35"/>
+      <c r="Z35" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA35" s="35"/>
       <c r="AB35" s="35"/>
       <c r="AC35" s="35"/>
@@ -12053,7 +12123,7 @@
       </c>
       <c r="G36" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36" s="42">
         <f t="shared" si="28"/>
@@ -12113,7 +12183,9 @@
       </c>
       <c r="X36" s="35"/>
       <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
+      <c r="Z36" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA36" s="35"/>
       <c r="AB36" s="35"/>
       <c r="AC36" s="35"/>
@@ -12256,7 +12328,7 @@
       </c>
       <c r="I37" s="42">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="42">
         <f t="shared" si="30"/>
@@ -12280,7 +12352,7 @@
       </c>
       <c r="O37" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P37" s="35" t="s">
         <v>38</v>
@@ -12308,7 +12380,9 @@
       </c>
       <c r="X37" s="35"/>
       <c r="Y37" s="35"/>
-      <c r="Z37" s="35"/>
+      <c r="Z37" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA37" s="35"/>
       <c r="AB37" s="35"/>
       <c r="AC37" s="35"/>
@@ -12443,7 +12517,7 @@
       </c>
       <c r="G38" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H38" s="42">
         <f t="shared" si="28"/>
@@ -12475,7 +12549,7 @@
       </c>
       <c r="O38" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P38" s="35" t="s">
         <v>38</v>
@@ -12503,7 +12577,9 @@
       </c>
       <c r="X38" s="35"/>
       <c r="Y38" s="35"/>
-      <c r="Z38" s="35"/>
+      <c r="Z38" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA38" s="35"/>
       <c r="AB38" s="35"/>
       <c r="AC38" s="35"/>
@@ -12638,7 +12714,7 @@
       </c>
       <c r="G39" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H39" s="42">
         <f t="shared" si="28"/>
@@ -12698,7 +12774,9 @@
       </c>
       <c r="X39" s="35"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="35"/>
+      <c r="Z39" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA39" s="35"/>
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
@@ -12833,7 +12911,7 @@
       </c>
       <c r="G40" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H40" s="42">
         <f t="shared" si="28"/>
@@ -12893,7 +12971,9 @@
       </c>
       <c r="X40" s="35"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="35"/>
+      <c r="Z40" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA40" s="35"/>
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
@@ -13028,7 +13108,7 @@
       </c>
       <c r="G41" s="41">
         <f t="shared" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H41" s="42">
         <f t="shared" si="28"/>
@@ -13060,7 +13140,7 @@
       </c>
       <c r="O41" s="34">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P41" s="35" t="s">
         <v>38</v>
@@ -13088,7 +13168,9 @@
       </c>
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
-      <c r="Z41" s="35"/>
+      <c r="Z41" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA41" s="35"/>
       <c r="AB41" s="35"/>
       <c r="AC41" s="35"/>
@@ -13223,7 +13305,7 @@
       </c>
       <c r="G42" s="41">
         <f t="shared" si="27"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H42" s="42">
         <f t="shared" si="28"/>
@@ -13255,7 +13337,7 @@
       </c>
       <c r="O42" s="34">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P42" s="35" t="s">
         <v>38</v>
@@ -13283,7 +13365,9 @@
       </c>
       <c r="X42" s="35"/>
       <c r="Y42" s="35"/>
-      <c r="Z42" s="35"/>
+      <c r="Z42" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA42" s="35"/>
       <c r="AB42" s="35"/>
       <c r="AC42" s="35"/>
@@ -13418,7 +13502,7 @@
       </c>
       <c r="G43" s="41">
         <f t="shared" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H43" s="42">
         <f t="shared" si="28"/>
@@ -13478,7 +13562,9 @@
       </c>
       <c r="X43" s="35"/>
       <c r="Y43" s="35"/>
-      <c r="Z43" s="35"/>
+      <c r="Z43" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA43" s="35"/>
       <c r="AB43" s="35"/>
       <c r="AC43" s="35"/>
@@ -13588,20 +13674,20 @@
       <c r="D44" s="75"/>
       <c r="E44" s="75"/>
       <c r="F44" s="74"/>
-      <c r="G44" s="200" t="s">
+      <c r="G44" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="H44" s="161"/>
-      <c r="I44" s="161"/>
-      <c r="J44" s="161"/>
-      <c r="K44" s="161"/>
-      <c r="L44" s="161"/>
-      <c r="M44" s="162"/>
-      <c r="N44" s="163" t="str">
+      <c r="H44" s="133"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="133"/>
+      <c r="M44" s="134"/>
+      <c r="N44" s="135" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O44" s="164"/>
+      <c r="O44" s="136"/>
       <c r="P44" s="43">
         <f>COUNTIF(P9:P43,"A")</f>
         <v>33</v>
@@ -13644,7 +13730,7 @@
       </c>
       <c r="Z44" s="43">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA44" s="43">
         <f t="shared" si="71"/>
@@ -13986,20 +14072,20 @@
       <c r="D45" s="75"/>
       <c r="E45" s="75"/>
       <c r="F45" s="74"/>
-      <c r="G45" s="170" t="s">
+      <c r="G45" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="161"/>
-      <c r="I45" s="161"/>
-      <c r="J45" s="161"/>
-      <c r="K45" s="161"/>
-      <c r="L45" s="161"/>
-      <c r="M45" s="162"/>
-      <c r="N45" s="163" t="str">
+      <c r="H45" s="133"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="133"/>
+      <c r="L45" s="133"/>
+      <c r="M45" s="134"/>
+      <c r="N45" s="135" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O45" s="164"/>
+      <c r="O45" s="136"/>
       <c r="P45" s="43">
         <f>COUNTIF(P9:P43,"CE")</f>
         <v>0</v>
@@ -14384,20 +14470,20 @@
       <c r="D46" s="75"/>
       <c r="E46" s="75"/>
       <c r="F46" s="74"/>
-      <c r="G46" s="171" t="s">
+      <c r="G46" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="161"/>
-      <c r="I46" s="161"/>
-      <c r="J46" s="161"/>
-      <c r="K46" s="161"/>
-      <c r="L46" s="161"/>
-      <c r="M46" s="162"/>
-      <c r="N46" s="163" t="str">
+      <c r="H46" s="133"/>
+      <c r="I46" s="133"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="133"/>
+      <c r="L46" s="133"/>
+      <c r="M46" s="134"/>
+      <c r="N46" s="135" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O46" s="164"/>
+      <c r="O46" s="136"/>
       <c r="P46" s="43">
         <f>COUNTIF(P9:P43,"SE")</f>
         <v>2</v>
@@ -14440,7 +14526,7 @@
       </c>
       <c r="Z46" s="43">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA46" s="43">
         <f t="shared" si="79"/>
@@ -14782,20 +14868,20 @@
       <c r="D47" s="75"/>
       <c r="E47" s="75"/>
       <c r="F47" s="44"/>
-      <c r="G47" s="172" t="s">
+      <c r="G47" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="H47" s="161"/>
-      <c r="I47" s="161"/>
-      <c r="J47" s="161"/>
-      <c r="K47" s="161"/>
-      <c r="L47" s="161"/>
-      <c r="M47" s="162"/>
-      <c r="N47" s="163" t="str">
+      <c r="H47" s="133"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="133"/>
+      <c r="L47" s="133"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="135" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O47" s="164"/>
+      <c r="O47" s="136"/>
       <c r="P47" s="43">
         <f>COUNTIF(P9:P43,"INC")</f>
         <v>0</v>
@@ -15180,20 +15266,20 @@
       <c r="D48" s="75"/>
       <c r="E48" s="75"/>
       <c r="F48" s="74"/>
-      <c r="G48" s="167" t="s">
+      <c r="G48" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="161"/>
-      <c r="I48" s="161"/>
-      <c r="J48" s="161"/>
-      <c r="K48" s="161"/>
-      <c r="L48" s="161"/>
-      <c r="M48" s="162"/>
-      <c r="N48" s="163" t="str">
+      <c r="H48" s="133"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="133"/>
+      <c r="M48" s="134"/>
+      <c r="N48" s="135" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O48" s="164"/>
+      <c r="O48" s="136"/>
       <c r="P48" s="43">
         <f>COUNTIF(P9:P43,"LIC")</f>
         <v>0</v>
@@ -15578,20 +15664,20 @@
       <c r="D49" s="75"/>
       <c r="E49" s="75"/>
       <c r="F49" s="74"/>
-      <c r="G49" s="160" t="s">
+      <c r="G49" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="H49" s="161"/>
-      <c r="I49" s="161"/>
-      <c r="J49" s="161"/>
-      <c r="K49" s="161"/>
-      <c r="L49" s="161"/>
-      <c r="M49" s="162"/>
-      <c r="N49" s="163" t="str">
+      <c r="H49" s="133"/>
+      <c r="I49" s="133"/>
+      <c r="J49" s="133"/>
+      <c r="K49" s="133"/>
+      <c r="L49" s="133"/>
+      <c r="M49" s="134"/>
+      <c r="N49" s="135" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O49" s="164"/>
+      <c r="O49" s="136"/>
       <c r="P49" s="43">
         <f>COUNTIF(P9:P43,"CLM")</f>
         <v>0</v>
@@ -15976,20 +16062,20 @@
       <c r="D50" s="75"/>
       <c r="E50" s="75"/>
       <c r="F50" s="74"/>
-      <c r="G50" s="165" t="s">
+      <c r="G50" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="H50" s="161"/>
-      <c r="I50" s="161"/>
-      <c r="J50" s="161"/>
-      <c r="K50" s="161"/>
-      <c r="L50" s="161"/>
-      <c r="M50" s="162"/>
-      <c r="N50" s="163" t="str">
+      <c r="H50" s="133"/>
+      <c r="I50" s="133"/>
+      <c r="J50" s="133"/>
+      <c r="K50" s="133"/>
+      <c r="L50" s="133"/>
+      <c r="M50" s="134"/>
+      <c r="N50" s="135" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O50" s="164"/>
+      <c r="O50" s="136"/>
       <c r="P50" s="43">
         <f>COUNTIF(P9:P43,"SFF")</f>
         <v>0</v>
@@ -16374,20 +16460,20 @@
       <c r="D51" s="75"/>
       <c r="E51" s="75"/>
       <c r="F51" s="74"/>
-      <c r="G51" s="166" t="s">
+      <c r="G51" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="H51" s="161"/>
-      <c r="I51" s="161"/>
-      <c r="J51" s="161"/>
-      <c r="K51" s="161"/>
-      <c r="L51" s="161"/>
-      <c r="M51" s="162"/>
-      <c r="N51" s="163" t="str">
+      <c r="H51" s="133"/>
+      <c r="I51" s="133"/>
+      <c r="J51" s="133"/>
+      <c r="K51" s="133"/>
+      <c r="L51" s="133"/>
+      <c r="M51" s="134"/>
+      <c r="N51" s="135" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O51" s="164"/>
+      <c r="O51" s="136"/>
       <c r="P51" s="43">
         <f>COUNTIF(P9:P43,"RET")</f>
         <v>0</v>
@@ -41728,11 +41814,65 @@
   </sheetData>
   <autoFilter ref="A8:DW51" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:O7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G44:M44"/>
-    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="AL1:AT1"/>
+    <mergeCell ref="AU1:BU1"/>
+    <mergeCell ref="BV1:CR1"/>
+    <mergeCell ref="AL3:AT3"/>
+    <mergeCell ref="CS1:CW5"/>
+    <mergeCell ref="AU2:BU2"/>
+    <mergeCell ref="BV2:CR2"/>
+    <mergeCell ref="BV3:CR3"/>
+    <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="CY1:DG1"/>
+    <mergeCell ref="CY2:DG2"/>
+    <mergeCell ref="CY4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="AU3:BU3"/>
+    <mergeCell ref="AU4:BU5"/>
+    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="DJ4:DK4"/>
+    <mergeCell ref="DL4:DR4"/>
+    <mergeCell ref="CX6:DW6"/>
+    <mergeCell ref="DL7:DM7"/>
+    <mergeCell ref="DN7:DO7"/>
+    <mergeCell ref="DP7:DQ7"/>
+    <mergeCell ref="DR7:DS7"/>
+    <mergeCell ref="DT7:DU7"/>
+    <mergeCell ref="DV7:DW7"/>
+    <mergeCell ref="CX7:CY7"/>
+    <mergeCell ref="CZ7:DA7"/>
+    <mergeCell ref="DB7:DC7"/>
+    <mergeCell ref="DD7:DE7"/>
+    <mergeCell ref="DF7:DG7"/>
+    <mergeCell ref="DH7:DI7"/>
+    <mergeCell ref="DJ7:DK7"/>
+    <mergeCell ref="G49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="G48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="G45:M45"/>
+    <mergeCell ref="G46:M46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="G47:M47"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="X1:AA1"/>
     <mergeCell ref="AB1:AK1"/>
     <mergeCell ref="AB2:AK2"/>
@@ -41749,65 +41889,11 @@
     <mergeCell ref="AB3:AK3"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="G1:O1"/>
-    <mergeCell ref="G48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="G45:M45"/>
-    <mergeCell ref="G46:M46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="G47:M47"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="G49:M49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="G50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="DJ4:DK4"/>
-    <mergeCell ref="DL4:DR4"/>
-    <mergeCell ref="CX6:DW6"/>
-    <mergeCell ref="DL7:DM7"/>
-    <mergeCell ref="DN7:DO7"/>
-    <mergeCell ref="DP7:DQ7"/>
-    <mergeCell ref="DR7:DS7"/>
-    <mergeCell ref="DT7:DU7"/>
-    <mergeCell ref="DV7:DW7"/>
-    <mergeCell ref="CX7:CY7"/>
-    <mergeCell ref="CZ7:DA7"/>
-    <mergeCell ref="DB7:DC7"/>
-    <mergeCell ref="DD7:DE7"/>
-    <mergeCell ref="DF7:DG7"/>
-    <mergeCell ref="DH7:DI7"/>
-    <mergeCell ref="DJ7:DK7"/>
-    <mergeCell ref="CY1:DG1"/>
-    <mergeCell ref="CY2:DG2"/>
-    <mergeCell ref="CY4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="AU3:BU3"/>
-    <mergeCell ref="AU4:BU5"/>
-    <mergeCell ref="BV4:CR5"/>
-    <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:BU1"/>
-    <mergeCell ref="BV1:CR1"/>
-    <mergeCell ref="AL3:AT3"/>
-    <mergeCell ref="CS1:CW5"/>
-    <mergeCell ref="AU2:BU2"/>
-    <mergeCell ref="BV2:CR2"/>
-    <mergeCell ref="BV3:CR3"/>
-    <mergeCell ref="AL2:AT2"/>
-    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:O7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G44:M44"/>
+    <mergeCell ref="N44:O44"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E43">
     <cfRule type="containsText" dxfId="80" priority="1" operator="containsText" text="RETIRADO">
@@ -42176,7 +42262,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="207">
+      <c r="A1" s="204">
         <v>0</v>
       </c>
       <c r="B1" s="147"/>
@@ -42187,7 +42273,7 @@
       <c r="G1" s="147"/>
       <c r="H1" s="147"/>
       <c r="I1" s="147"/>
-      <c r="J1" s="133"/>
+      <c r="J1" s="198"/>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
       <c r="N1" s="48"/>
@@ -42214,7 +42300,7 @@
       <c r="G2" s="147"/>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
-      <c r="J2" s="133"/>
+      <c r="J2" s="198"/>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
@@ -42232,15 +42318,15 @@
       <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:26" ht="15.75">
-      <c r="A3" s="201" t="s">
+      <c r="A3" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="208" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="205" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="127"/>
-      <c r="E3" s="177"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="50"/>
@@ -42264,15 +42350,15 @@
       <c r="Z3" s="48"/>
     </row>
     <row r="4" spans="1:26" ht="15.75">
-      <c r="A4" s="201" t="s">
+      <c r="A4" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="177"/>
-      <c r="C4" s="209">
+      <c r="B4" s="124"/>
+      <c r="C4" s="206">
         <v>3414937</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="177"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
       <c r="F4" s="51" t="s">
         <v>65</v>
       </c>
@@ -42302,15 +42388,15 @@
       <c r="Z4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15.75">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="177"/>
-      <c r="C5" s="206" t="s">
+      <c r="B5" s="124"/>
+      <c r="C5" s="203" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="127"/>
-      <c r="E5" s="177"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="124"/>
       <c r="F5" s="51" t="s">
         <v>67</v>
       </c>
@@ -42338,15 +42424,15 @@
       <c r="Z5" s="48"/>
     </row>
     <row r="6" spans="1:26" ht="15.75">
-      <c r="A6" s="201" t="s">
+      <c r="A6" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="177"/>
-      <c r="C6" s="202" t="s">
+      <c r="B6" s="124"/>
+      <c r="C6" s="207" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="127"/>
-      <c r="E6" s="177"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="124"/>
       <c r="F6" s="51" t="s">
         <v>69</v>
       </c>
@@ -42374,15 +42460,15 @@
       <c r="Z6" s="48"/>
     </row>
     <row r="7" spans="1:26" ht="15.75">
-      <c r="A7" s="201" t="s">
+      <c r="A7" s="202" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="177"/>
-      <c r="C7" s="203" t="s">
+      <c r="B7" s="124"/>
+      <c r="C7" s="208" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="127"/>
-      <c r="E7" s="177"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="124"/>
       <c r="F7" s="55" t="s">
         <v>70</v>
       </c>
@@ -42410,17 +42496,17 @@
       <c r="Z7" s="48"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="177"/>
-      <c r="C8" s="205" t="s">
+      <c r="B8" s="124"/>
+      <c r="C8" s="210" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="177"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="48"/>
@@ -43251,7 +43337,7 @@
       <c r="H25" s="84" t="s">
         <v>205</v>
       </c>
-      <c r="I25" s="214" t="s">
+      <c r="I25" s="121" t="s">
         <v>206</v>
       </c>
       <c r="J25" s="82">
@@ -52835,6 +52921,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A1:J2"/>
@@ -52842,12 +52934,6 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="B45:B49">
     <cfRule type="expression" dxfId="15" priority="1">
@@ -53048,12 +53134,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="211" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
       <c r="E1" s="62"/>
       <c r="F1" s="62"/>
     </row>
@@ -53072,7 +53158,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="212" t="s">
         <v>356</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -53086,7 +53172,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="211"/>
+      <c r="A4" s="213"/>
       <c r="B4" s="66" t="s">
         <v>278</v>
       </c>
@@ -53098,7 +53184,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="211"/>
+      <c r="A5" s="213"/>
       <c r="B5" s="66" t="s">
         <v>280</v>
       </c>
@@ -53110,7 +53196,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="211"/>
+      <c r="A6" s="213"/>
       <c r="B6" s="66" t="s">
         <v>282</v>
       </c>
@@ -53122,7 +53208,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="212"/>
+      <c r="A7" s="214"/>
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
       <c r="D7" s="69"/>
@@ -53145,7 +53231,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="210" t="s">
+      <c r="A10" s="212" t="s">
         <v>357</v>
       </c>
       <c r="B10" s="66" t="s">
@@ -53159,7 +53245,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="211"/>
+      <c r="A11" s="213"/>
       <c r="B11" s="66" t="s">
         <v>286</v>
       </c>
@@ -53171,7 +53257,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="211"/>
+      <c r="A12" s="213"/>
       <c r="B12" s="66" t="s">
         <v>291</v>
       </c>
@@ -53183,13 +53269,13 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="211"/>
+      <c r="A13" s="213"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="113"/>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="212"/>
+      <c r="A14" s="214"/>
       <c r="B14" s="68"/>
       <c r="C14" s="68"/>
       <c r="D14" s="69"/>
@@ -53209,7 +53295,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="210" t="s">
+      <c r="A17" s="212" t="s">
         <v>358</v>
       </c>
       <c r="B17" s="66" t="s">
@@ -53223,7 +53309,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="211"/>
+      <c r="A18" s="213"/>
       <c r="B18" s="66" t="s">
         <v>295</v>
       </c>
@@ -53235,7 +53321,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="211"/>
+      <c r="A19" s="213"/>
       <c r="B19" s="66" t="s">
         <v>297</v>
       </c>
@@ -53247,7 +53333,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="211"/>
+      <c r="A20" s="213"/>
       <c r="B20" s="66" t="s">
         <v>299</v>
       </c>
@@ -53259,7 +53345,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="212"/>
+      <c r="A21" s="214"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68"/>
       <c r="D21" s="69"/>
@@ -53279,7 +53365,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="210" t="s">
+      <c r="A24" s="212" t="s">
         <v>359</v>
       </c>
       <c r="B24" s="66" t="s">
@@ -53293,7 +53379,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="211"/>
+      <c r="A25" s="213"/>
       <c r="B25" s="66" t="s">
         <v>304</v>
       </c>
@@ -53305,7 +53391,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="211"/>
+      <c r="A26" s="213"/>
       <c r="B26" s="66" t="s">
         <v>306</v>
       </c>
@@ -53317,7 +53403,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="211"/>
+      <c r="A27" s="213"/>
       <c r="B27" s="66" t="s">
         <v>307</v>
       </c>
@@ -53329,7 +53415,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="212"/>
+      <c r="A28" s="214"/>
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
       <c r="D28" s="69"/>
@@ -53349,7 +53435,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="210" t="s">
+      <c r="A31" s="212" t="s">
         <v>360</v>
       </c>
       <c r="B31" s="66" t="s">
@@ -53363,7 +53449,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="211"/>
+      <c r="A32" s="213"/>
       <c r="B32" s="66" t="s">
         <v>311</v>
       </c>
@@ -53375,7 +53461,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="211"/>
+      <c r="A33" s="213"/>
       <c r="B33" s="66" t="s">
         <v>313</v>
       </c>
@@ -53387,7 +53473,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="211"/>
+      <c r="A34" s="213"/>
       <c r="B34" s="66" t="s">
         <v>315</v>
       </c>
@@ -53399,7 +53485,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="212"/>
+      <c r="A35" s="214"/>
       <c r="B35" s="68"/>
       <c r="C35" s="68"/>
       <c r="D35" s="69"/>
@@ -53419,7 +53505,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="210" t="s">
+      <c r="A38" s="212" t="s">
         <v>361</v>
       </c>
       <c r="B38" s="66" t="s">
@@ -53433,7 +53519,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="211"/>
+      <c r="A39" s="213"/>
       <c r="B39" s="66" t="s">
         <v>319</v>
       </c>
@@ -53445,7 +53531,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="211"/>
+      <c r="A40" s="213"/>
       <c r="B40" s="66" t="s">
         <v>320</v>
       </c>
@@ -53457,7 +53543,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="211"/>
+      <c r="A41" s="213"/>
       <c r="B41" s="66" t="s">
         <v>288</v>
       </c>
@@ -53469,7 +53555,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="212"/>
+      <c r="A42" s="214"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
       <c r="D42" s="69"/>
@@ -53490,7 +53576,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
-      <c r="A45" s="210" t="s">
+      <c r="A45" s="212" t="s">
         <v>362</v>
       </c>
       <c r="B45" s="66" t="s">
@@ -53504,7 +53590,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="211"/>
+      <c r="A46" s="213"/>
       <c r="B46" s="66" t="s">
         <v>324</v>
       </c>
@@ -53516,7 +53602,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="211"/>
+      <c r="A47" s="213"/>
       <c r="B47" s="66" t="s">
         <v>326</v>
       </c>
@@ -53528,7 +53614,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="211"/>
+      <c r="A48" s="213"/>
       <c r="B48" s="66" t="s">
         <v>328</v>
       </c>
@@ -53540,7 +53626,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="212"/>
+      <c r="A49" s="214"/>
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
       <c r="D49" s="69"/>
@@ -53561,7 +53647,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
-      <c r="A52" s="210" t="s">
+      <c r="A52" s="212" t="s">
         <v>363</v>
       </c>
       <c r="B52" s="66" t="s">
@@ -53575,7 +53661,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
-      <c r="A53" s="211"/>
+      <c r="A53" s="213"/>
       <c r="B53" s="66" t="s">
         <v>332</v>
       </c>
@@ -53587,7 +53673,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
-      <c r="A54" s="211"/>
+      <c r="A54" s="213"/>
       <c r="B54" s="66" t="s">
         <v>334</v>
       </c>
@@ -53599,7 +53685,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
-      <c r="A55" s="211"/>
+      <c r="A55" s="213"/>
       <c r="B55" s="66" t="s">
         <v>336</v>
       </c>
@@ -53611,7 +53697,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="212"/>
+      <c r="A56" s="214"/>
       <c r="B56" s="68" t="s">
         <v>339</v>
       </c>
@@ -53638,7 +53724,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="210" t="s">
+      <c r="A59" s="212" t="s">
         <v>364</v>
       </c>
       <c r="B59" s="66" t="s">
@@ -53652,7 +53738,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1">
-      <c r="A60" s="211"/>
+      <c r="A60" s="213"/>
       <c r="B60" s="66" t="s">
         <v>345</v>
       </c>
@@ -53664,35 +53750,35 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1">
-      <c r="A61" s="211"/>
+      <c r="A61" s="213"/>
       <c r="B61" s="66"/>
       <c r="C61" s="66"/>
       <c r="D61" s="113"/>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1">
-      <c r="A62" s="211"/>
+      <c r="A62" s="213"/>
       <c r="B62" s="66"/>
       <c r="C62" s="66"/>
       <c r="D62" s="67"/>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="212"/>
+      <c r="A63" s="214"/>
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
       <c r="D63" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A38:A42"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A59:A63"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A38:A42"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{BF44E5AF-C41E-4FE1-AB09-EC39BA924783}"/>

--- a/assets/Listados/CGS - 3414937 - 2026.xlsx
+++ b/assets/Listados/CGS - 3414937 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB5693-EC90-4B0F-8986-ACFDF6794C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A716324-4340-48B4-8A9F-211DD3F91A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -3085,23 +3085,94 @@
     <xf numFmtId="0" fontId="56" fillId="16" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3110,77 +3181,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3194,81 +3205,92 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3282,36 +3304,14 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4754,125 +4754,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="158"/>
-      <c r="B1" s="127"/>
-      <c r="C1" s="159" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="163" t="s">
+      <c r="A1" s="198"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="202" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="123"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="123"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="138"/>
-      <c r="V1" s="138"/>
-      <c r="W1" s="138"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="138"/>
-      <c r="Z1" s="138"/>
-      <c r="AA1" s="138"/>
-      <c r="AB1" s="139"/>
-      <c r="AC1" s="138"/>
-      <c r="AD1" s="138"/>
-      <c r="AE1" s="138"/>
-      <c r="AF1" s="138"/>
-      <c r="AG1" s="138"/>
-      <c r="AH1" s="138"/>
-      <c r="AI1" s="138"/>
-      <c r="AJ1" s="138"/>
-      <c r="AK1" s="140"/>
-      <c r="AL1" s="190"/>
-      <c r="AM1" s="138"/>
-      <c r="AN1" s="138"/>
-      <c r="AO1" s="138"/>
-      <c r="AP1" s="138"/>
-      <c r="AQ1" s="138"/>
-      <c r="AR1" s="138"/>
-      <c r="AS1" s="138"/>
-      <c r="AT1" s="138"/>
-      <c r="AU1" s="191"/>
-      <c r="AV1" s="138"/>
-      <c r="AW1" s="138"/>
-      <c r="AX1" s="138"/>
-      <c r="AY1" s="138"/>
-      <c r="AZ1" s="138"/>
-      <c r="BA1" s="138"/>
-      <c r="BB1" s="138"/>
-      <c r="BC1" s="138"/>
-      <c r="BD1" s="138"/>
-      <c r="BE1" s="138"/>
-      <c r="BF1" s="138"/>
-      <c r="BG1" s="138"/>
-      <c r="BH1" s="138"/>
-      <c r="BI1" s="138"/>
-      <c r="BJ1" s="138"/>
-      <c r="BK1" s="138"/>
-      <c r="BL1" s="138"/>
-      <c r="BM1" s="138"/>
-      <c r="BN1" s="138"/>
-      <c r="BO1" s="138"/>
-      <c r="BP1" s="138"/>
-      <c r="BQ1" s="138"/>
-      <c r="BR1" s="138"/>
-      <c r="BS1" s="138"/>
-      <c r="BT1" s="138"/>
-      <c r="BU1" s="138"/>
-      <c r="BV1" s="192"/>
-      <c r="BW1" s="138"/>
-      <c r="BX1" s="138"/>
-      <c r="BY1" s="138"/>
-      <c r="BZ1" s="138"/>
-      <c r="CA1" s="138"/>
-      <c r="CB1" s="138"/>
-      <c r="CC1" s="138"/>
-      <c r="CD1" s="138"/>
-      <c r="CE1" s="138"/>
-      <c r="CF1" s="138"/>
-      <c r="CG1" s="138"/>
-      <c r="CH1" s="138"/>
-      <c r="CI1" s="138"/>
-      <c r="CJ1" s="138"/>
-      <c r="CK1" s="138"/>
-      <c r="CL1" s="138"/>
-      <c r="CM1" s="138"/>
-      <c r="CN1" s="138"/>
-      <c r="CO1" s="138"/>
-      <c r="CP1" s="138"/>
-      <c r="CQ1" s="138"/>
-      <c r="CR1" s="140"/>
-      <c r="CS1" s="194" t="s">
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="185"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="186"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="187"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="186"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="130"/>
+      <c r="AL1" s="126"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="127"/>
+      <c r="AT1" s="127"/>
+      <c r="AU1" s="128"/>
+      <c r="AV1" s="127"/>
+      <c r="AW1" s="127"/>
+      <c r="AX1" s="127"/>
+      <c r="AY1" s="127"/>
+      <c r="AZ1" s="127"/>
+      <c r="BA1" s="127"/>
+      <c r="BB1" s="127"/>
+      <c r="BC1" s="127"/>
+      <c r="BD1" s="127"/>
+      <c r="BE1" s="127"/>
+      <c r="BF1" s="127"/>
+      <c r="BG1" s="127"/>
+      <c r="BH1" s="127"/>
+      <c r="BI1" s="127"/>
+      <c r="BJ1" s="127"/>
+      <c r="BK1" s="127"/>
+      <c r="BL1" s="127"/>
+      <c r="BM1" s="127"/>
+      <c r="BN1" s="127"/>
+      <c r="BO1" s="127"/>
+      <c r="BP1" s="127"/>
+      <c r="BQ1" s="127"/>
+      <c r="BR1" s="127"/>
+      <c r="BS1" s="127"/>
+      <c r="BT1" s="127"/>
+      <c r="BU1" s="127"/>
+      <c r="BV1" s="129"/>
+      <c r="BW1" s="127"/>
+      <c r="BX1" s="127"/>
+      <c r="BY1" s="127"/>
+      <c r="BZ1" s="127"/>
+      <c r="CA1" s="127"/>
+      <c r="CB1" s="127"/>
+      <c r="CC1" s="127"/>
+      <c r="CD1" s="127"/>
+      <c r="CE1" s="127"/>
+      <c r="CF1" s="127"/>
+      <c r="CG1" s="127"/>
+      <c r="CH1" s="127"/>
+      <c r="CI1" s="127"/>
+      <c r="CJ1" s="127"/>
+      <c r="CK1" s="127"/>
+      <c r="CL1" s="127"/>
+      <c r="CM1" s="127"/>
+      <c r="CN1" s="127"/>
+      <c r="CO1" s="127"/>
+      <c r="CP1" s="127"/>
+      <c r="CQ1" s="127"/>
+      <c r="CR1" s="130"/>
+      <c r="CS1" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="195"/>
-      <c r="CU1" s="195"/>
-      <c r="CV1" s="195"/>
-      <c r="CW1" s="196"/>
+      <c r="CT1" s="134"/>
+      <c r="CU1" s="134"/>
+      <c r="CV1" s="134"/>
+      <c r="CW1" s="135"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="184" t="s">
+      <c r="CY1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="185"/>
-      <c r="DA1" s="185"/>
-      <c r="DB1" s="185"/>
-      <c r="DC1" s="185"/>
-      <c r="DD1" s="185"/>
-      <c r="DE1" s="185"/>
-      <c r="DF1" s="185"/>
-      <c r="DG1" s="185"/>
+      <c r="CZ1" s="137"/>
+      <c r="DA1" s="137"/>
+      <c r="DB1" s="137"/>
+      <c r="DC1" s="137"/>
+      <c r="DD1" s="137"/>
+      <c r="DE1" s="137"/>
+      <c r="DF1" s="137"/>
+      <c r="DG1" s="137"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4891,122 +4891,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="128"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="163" t="s">
+      <c r="A2" s="200"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="165"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="142"/>
-      <c r="X2" s="166"/>
-      <c r="Y2" s="123"/>
-      <c r="Z2" s="123"/>
-      <c r="AA2" s="123"/>
-      <c r="AB2" s="141"/>
-      <c r="AC2" s="123"/>
-      <c r="AD2" s="123"/>
-      <c r="AE2" s="123"/>
-      <c r="AF2" s="123"/>
-      <c r="AG2" s="123"/>
-      <c r="AH2" s="123"/>
-      <c r="AI2" s="123"/>
-      <c r="AJ2" s="123"/>
-      <c r="AK2" s="142"/>
-      <c r="AL2" s="166"/>
-      <c r="AM2" s="123"/>
-      <c r="AN2" s="123"/>
-      <c r="AO2" s="123"/>
-      <c r="AP2" s="123"/>
-      <c r="AQ2" s="123"/>
-      <c r="AR2" s="123"/>
-      <c r="AS2" s="123"/>
-      <c r="AT2" s="123"/>
-      <c r="AU2" s="165"/>
-      <c r="AV2" s="123"/>
-      <c r="AW2" s="123"/>
-      <c r="AX2" s="123"/>
-      <c r="AY2" s="123"/>
-      <c r="AZ2" s="123"/>
-      <c r="BA2" s="123"/>
-      <c r="BB2" s="123"/>
-      <c r="BC2" s="123"/>
-      <c r="BD2" s="123"/>
-      <c r="BE2" s="123"/>
-      <c r="BF2" s="123"/>
-      <c r="BG2" s="123"/>
-      <c r="BH2" s="123"/>
-      <c r="BI2" s="123"/>
-      <c r="BJ2" s="123"/>
-      <c r="BK2" s="123"/>
-      <c r="BL2" s="123"/>
-      <c r="BM2" s="123"/>
-      <c r="BN2" s="123"/>
-      <c r="BO2" s="123"/>
-      <c r="BP2" s="123"/>
-      <c r="BQ2" s="123"/>
-      <c r="BR2" s="123"/>
-      <c r="BS2" s="123"/>
-      <c r="BT2" s="123"/>
-      <c r="BU2" s="123"/>
-      <c r="BV2" s="199"/>
-      <c r="BW2" s="123"/>
-      <c r="BX2" s="123"/>
-      <c r="BY2" s="123"/>
-      <c r="BZ2" s="123"/>
-      <c r="CA2" s="123"/>
-      <c r="CB2" s="123"/>
-      <c r="CC2" s="123"/>
-      <c r="CD2" s="123"/>
-      <c r="CE2" s="123"/>
-      <c r="CF2" s="123"/>
-      <c r="CG2" s="123"/>
-      <c r="CH2" s="123"/>
-      <c r="CI2" s="123"/>
-      <c r="CJ2" s="123"/>
-      <c r="CK2" s="123"/>
-      <c r="CL2" s="123"/>
-      <c r="CM2" s="123"/>
-      <c r="CN2" s="123"/>
-      <c r="CO2" s="123"/>
-      <c r="CP2" s="123"/>
-      <c r="CQ2" s="123"/>
-      <c r="CR2" s="142"/>
-      <c r="CS2" s="197"/>
-      <c r="CT2" s="185"/>
-      <c r="CU2" s="185"/>
-      <c r="CV2" s="185"/>
-      <c r="CW2" s="198"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="179"/>
+      <c r="Q2" s="180"/>
+      <c r="R2" s="180"/>
+      <c r="S2" s="180"/>
+      <c r="T2" s="142"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="132"/>
+      <c r="AA2" s="132"/>
+      <c r="AB2" s="188"/>
+      <c r="AC2" s="132"/>
+      <c r="AD2" s="132"/>
+      <c r="AE2" s="132"/>
+      <c r="AF2" s="132"/>
+      <c r="AG2" s="132"/>
+      <c r="AH2" s="132"/>
+      <c r="AI2" s="132"/>
+      <c r="AJ2" s="132"/>
+      <c r="AK2" s="144"/>
+      <c r="AL2" s="146"/>
+      <c r="AM2" s="132"/>
+      <c r="AN2" s="132"/>
+      <c r="AO2" s="132"/>
+      <c r="AP2" s="132"/>
+      <c r="AQ2" s="132"/>
+      <c r="AR2" s="132"/>
+      <c r="AS2" s="132"/>
+      <c r="AT2" s="132"/>
+      <c r="AU2" s="142"/>
+      <c r="AV2" s="132"/>
+      <c r="AW2" s="132"/>
+      <c r="AX2" s="132"/>
+      <c r="AY2" s="132"/>
+      <c r="AZ2" s="132"/>
+      <c r="BA2" s="132"/>
+      <c r="BB2" s="132"/>
+      <c r="BC2" s="132"/>
+      <c r="BD2" s="132"/>
+      <c r="BE2" s="132"/>
+      <c r="BF2" s="132"/>
+      <c r="BG2" s="132"/>
+      <c r="BH2" s="132"/>
+      <c r="BI2" s="132"/>
+      <c r="BJ2" s="132"/>
+      <c r="BK2" s="132"/>
+      <c r="BL2" s="132"/>
+      <c r="BM2" s="132"/>
+      <c r="BN2" s="132"/>
+      <c r="BO2" s="132"/>
+      <c r="BP2" s="132"/>
+      <c r="BQ2" s="132"/>
+      <c r="BR2" s="132"/>
+      <c r="BS2" s="132"/>
+      <c r="BT2" s="132"/>
+      <c r="BU2" s="132"/>
+      <c r="BV2" s="143"/>
+      <c r="BW2" s="132"/>
+      <c r="BX2" s="132"/>
+      <c r="BY2" s="132"/>
+      <c r="BZ2" s="132"/>
+      <c r="CA2" s="132"/>
+      <c r="CB2" s="132"/>
+      <c r="CC2" s="132"/>
+      <c r="CD2" s="132"/>
+      <c r="CE2" s="132"/>
+      <c r="CF2" s="132"/>
+      <c r="CG2" s="132"/>
+      <c r="CH2" s="132"/>
+      <c r="CI2" s="132"/>
+      <c r="CJ2" s="132"/>
+      <c r="CK2" s="132"/>
+      <c r="CL2" s="132"/>
+      <c r="CM2" s="132"/>
+      <c r="CN2" s="132"/>
+      <c r="CO2" s="132"/>
+      <c r="CP2" s="132"/>
+      <c r="CQ2" s="132"/>
+      <c r="CR2" s="144"/>
+      <c r="CS2" s="136"/>
+      <c r="CT2" s="137"/>
+      <c r="CU2" s="137"/>
+      <c r="CV2" s="137"/>
+      <c r="CW2" s="138"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="186">
+      <c r="CY2" s="151">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>35</v>
       </c>
-      <c r="CZ2" s="147"/>
-      <c r="DA2" s="147"/>
-      <c r="DB2" s="147"/>
-      <c r="DC2" s="147"/>
-      <c r="DD2" s="147"/>
-      <c r="DE2" s="147"/>
-      <c r="DF2" s="147"/>
-      <c r="DG2" s="147"/>
+      <c r="CZ2" s="152"/>
+      <c r="DA2" s="152"/>
+      <c r="DB2" s="152"/>
+      <c r="DC2" s="152"/>
+      <c r="DD2" s="152"/>
+      <c r="DE2" s="152"/>
+      <c r="DF2" s="152"/>
+      <c r="DG2" s="152"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -5025,113 +5025,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="181" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="160" t="s">
+      <c r="B3" s="132"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="183" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="123"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="144" t="s">
+      <c r="E3" s="132"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="123"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="123"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="142"/>
-      <c r="X3" s="167"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="123"/>
-      <c r="AA3" s="123"/>
-      <c r="AB3" s="157"/>
-      <c r="AC3" s="123"/>
-      <c r="AD3" s="123"/>
-      <c r="AE3" s="123"/>
-      <c r="AF3" s="123"/>
-      <c r="AG3" s="123"/>
-      <c r="AH3" s="123"/>
-      <c r="AI3" s="123"/>
-      <c r="AJ3" s="123"/>
-      <c r="AK3" s="142"/>
-      <c r="AL3" s="193"/>
-      <c r="AM3" s="123"/>
-      <c r="AN3" s="123"/>
-      <c r="AO3" s="123"/>
-      <c r="AP3" s="123"/>
-      <c r="AQ3" s="123"/>
-      <c r="AR3" s="123"/>
-      <c r="AS3" s="123"/>
-      <c r="AT3" s="123"/>
-      <c r="AU3" s="187"/>
-      <c r="AV3" s="123"/>
-      <c r="AW3" s="123"/>
-      <c r="AX3" s="123"/>
-      <c r="AY3" s="123"/>
-      <c r="AZ3" s="123"/>
-      <c r="BA3" s="123"/>
-      <c r="BB3" s="123"/>
-      <c r="BC3" s="123"/>
-      <c r="BD3" s="123"/>
-      <c r="BE3" s="123"/>
-      <c r="BF3" s="123"/>
-      <c r="BG3" s="123"/>
-      <c r="BH3" s="123"/>
-      <c r="BI3" s="123"/>
-      <c r="BJ3" s="123"/>
-      <c r="BK3" s="123"/>
-      <c r="BL3" s="123"/>
-      <c r="BM3" s="123"/>
-      <c r="BN3" s="123"/>
-      <c r="BO3" s="123"/>
-      <c r="BP3" s="123"/>
-      <c r="BQ3" s="123"/>
-      <c r="BR3" s="123"/>
-      <c r="BS3" s="123"/>
-      <c r="BT3" s="123"/>
-      <c r="BU3" s="123"/>
-      <c r="BV3" s="200"/>
-      <c r="BW3" s="123"/>
-      <c r="BX3" s="123"/>
-      <c r="BY3" s="123"/>
-      <c r="BZ3" s="123"/>
-      <c r="CA3" s="123"/>
-      <c r="CB3" s="123"/>
-      <c r="CC3" s="123"/>
-      <c r="CD3" s="123"/>
-      <c r="CE3" s="123"/>
-      <c r="CF3" s="123"/>
-      <c r="CG3" s="123"/>
-      <c r="CH3" s="123"/>
-      <c r="CI3" s="123"/>
-      <c r="CJ3" s="123"/>
-      <c r="CK3" s="123"/>
-      <c r="CL3" s="123"/>
-      <c r="CM3" s="123"/>
-      <c r="CN3" s="123"/>
-      <c r="CO3" s="123"/>
-      <c r="CP3" s="123"/>
-      <c r="CQ3" s="123"/>
-      <c r="CR3" s="142"/>
-      <c r="CS3" s="197"/>
-      <c r="CT3" s="185"/>
-      <c r="CU3" s="185"/>
-      <c r="CV3" s="185"/>
-      <c r="CW3" s="198"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="184"/>
+      <c r="Q3" s="132"/>
+      <c r="R3" s="132"/>
+      <c r="S3" s="132"/>
+      <c r="T3" s="173"/>
+      <c r="U3" s="132"/>
+      <c r="V3" s="132"/>
+      <c r="W3" s="144"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="132"/>
+      <c r="Z3" s="132"/>
+      <c r="AA3" s="132"/>
+      <c r="AB3" s="173"/>
+      <c r="AC3" s="132"/>
+      <c r="AD3" s="132"/>
+      <c r="AE3" s="132"/>
+      <c r="AF3" s="132"/>
+      <c r="AG3" s="132"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="132"/>
+      <c r="AJ3" s="132"/>
+      <c r="AK3" s="144"/>
+      <c r="AL3" s="131"/>
+      <c r="AM3" s="132"/>
+      <c r="AN3" s="132"/>
+      <c r="AO3" s="132"/>
+      <c r="AP3" s="132"/>
+      <c r="AQ3" s="132"/>
+      <c r="AR3" s="132"/>
+      <c r="AS3" s="132"/>
+      <c r="AT3" s="132"/>
+      <c r="AU3" s="157"/>
+      <c r="AV3" s="132"/>
+      <c r="AW3" s="132"/>
+      <c r="AX3" s="132"/>
+      <c r="AY3" s="132"/>
+      <c r="AZ3" s="132"/>
+      <c r="BA3" s="132"/>
+      <c r="BB3" s="132"/>
+      <c r="BC3" s="132"/>
+      <c r="BD3" s="132"/>
+      <c r="BE3" s="132"/>
+      <c r="BF3" s="132"/>
+      <c r="BG3" s="132"/>
+      <c r="BH3" s="132"/>
+      <c r="BI3" s="132"/>
+      <c r="BJ3" s="132"/>
+      <c r="BK3" s="132"/>
+      <c r="BL3" s="132"/>
+      <c r="BM3" s="132"/>
+      <c r="BN3" s="132"/>
+      <c r="BO3" s="132"/>
+      <c r="BP3" s="132"/>
+      <c r="BQ3" s="132"/>
+      <c r="BR3" s="132"/>
+      <c r="BS3" s="132"/>
+      <c r="BT3" s="132"/>
+      <c r="BU3" s="132"/>
+      <c r="BV3" s="145"/>
+      <c r="BW3" s="132"/>
+      <c r="BX3" s="132"/>
+      <c r="BY3" s="132"/>
+      <c r="BZ3" s="132"/>
+      <c r="CA3" s="132"/>
+      <c r="CB3" s="132"/>
+      <c r="CC3" s="132"/>
+      <c r="CD3" s="132"/>
+      <c r="CE3" s="132"/>
+      <c r="CF3" s="132"/>
+      <c r="CG3" s="132"/>
+      <c r="CH3" s="132"/>
+      <c r="CI3" s="132"/>
+      <c r="CJ3" s="132"/>
+      <c r="CK3" s="132"/>
+      <c r="CL3" s="132"/>
+      <c r="CM3" s="132"/>
+      <c r="CN3" s="132"/>
+      <c r="CO3" s="132"/>
+      <c r="CP3" s="132"/>
+      <c r="CQ3" s="132"/>
+      <c r="CR3" s="144"/>
+      <c r="CS3" s="136"/>
+      <c r="CT3" s="137"/>
+      <c r="CU3" s="137"/>
+      <c r="CV3" s="137"/>
+      <c r="CW3" s="138"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -5160,142 +5160,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="122" t="s">
+      <c r="A4" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="143" t="s">
+      <c r="B4" s="132"/>
+      <c r="C4" s="182"/>
+      <c r="D4" s="189" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="123"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="145" t="s">
+      <c r="E4" s="132"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
-      <c r="S4" s="126"/>
-      <c r="T4" s="151"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="126"/>
-      <c r="W4" s="152"/>
-      <c r="X4" s="154"/>
-      <c r="Y4" s="126"/>
-      <c r="Z4" s="126"/>
-      <c r="AA4" s="126"/>
-      <c r="AB4" s="155"/>
-      <c r="AC4" s="126"/>
-      <c r="AD4" s="126"/>
-      <c r="AE4" s="126"/>
-      <c r="AF4" s="126"/>
-      <c r="AG4" s="126"/>
-      <c r="AH4" s="126"/>
-      <c r="AI4" s="126"/>
-      <c r="AJ4" s="126"/>
-      <c r="AK4" s="152"/>
-      <c r="AL4" s="201"/>
-      <c r="AM4" s="126"/>
-      <c r="AN4" s="126"/>
-      <c r="AO4" s="126"/>
-      <c r="AP4" s="126"/>
-      <c r="AQ4" s="126"/>
-      <c r="AR4" s="126"/>
-      <c r="AS4" s="126"/>
-      <c r="AT4" s="152"/>
-      <c r="AU4" s="188"/>
-      <c r="AV4" s="126"/>
-      <c r="AW4" s="126"/>
-      <c r="AX4" s="126"/>
-      <c r="AY4" s="126"/>
-      <c r="AZ4" s="126"/>
-      <c r="BA4" s="126"/>
-      <c r="BB4" s="126"/>
-      <c r="BC4" s="126"/>
-      <c r="BD4" s="126"/>
-      <c r="BE4" s="126"/>
-      <c r="BF4" s="126"/>
-      <c r="BG4" s="126"/>
-      <c r="BH4" s="126"/>
-      <c r="BI4" s="126"/>
-      <c r="BJ4" s="126"/>
-      <c r="BK4" s="126"/>
-      <c r="BL4" s="126"/>
-      <c r="BM4" s="126"/>
-      <c r="BN4" s="126"/>
-      <c r="BO4" s="126"/>
-      <c r="BP4" s="126"/>
-      <c r="BQ4" s="126"/>
-      <c r="BR4" s="126"/>
-      <c r="BS4" s="126"/>
-      <c r="BT4" s="126"/>
-      <c r="BU4" s="126"/>
-      <c r="BV4" s="189"/>
-      <c r="BW4" s="126"/>
-      <c r="BX4" s="126"/>
-      <c r="BY4" s="126"/>
-      <c r="BZ4" s="126"/>
-      <c r="CA4" s="126"/>
-      <c r="CB4" s="126"/>
-      <c r="CC4" s="126"/>
-      <c r="CD4" s="126"/>
-      <c r="CE4" s="126"/>
-      <c r="CF4" s="126"/>
-      <c r="CG4" s="126"/>
-      <c r="CH4" s="126"/>
-      <c r="CI4" s="126"/>
-      <c r="CJ4" s="126"/>
-      <c r="CK4" s="126"/>
-      <c r="CL4" s="126"/>
-      <c r="CM4" s="126"/>
-      <c r="CN4" s="126"/>
-      <c r="CO4" s="126"/>
-      <c r="CP4" s="126"/>
-      <c r="CQ4" s="126"/>
-      <c r="CR4" s="152"/>
-      <c r="CS4" s="197"/>
-      <c r="CT4" s="185"/>
-      <c r="CU4" s="185"/>
-      <c r="CV4" s="185"/>
-      <c r="CW4" s="198"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="148"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="193"/>
+      <c r="Q4" s="148"/>
+      <c r="R4" s="148"/>
+      <c r="S4" s="148"/>
+      <c r="T4" s="194"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="148"/>
+      <c r="W4" s="149"/>
+      <c r="X4" s="195"/>
+      <c r="Y4" s="148"/>
+      <c r="Z4" s="148"/>
+      <c r="AA4" s="148"/>
+      <c r="AB4" s="196"/>
+      <c r="AC4" s="148"/>
+      <c r="AD4" s="148"/>
+      <c r="AE4" s="148"/>
+      <c r="AF4" s="148"/>
+      <c r="AG4" s="148"/>
+      <c r="AH4" s="148"/>
+      <c r="AI4" s="148"/>
+      <c r="AJ4" s="148"/>
+      <c r="AK4" s="149"/>
+      <c r="AL4" s="147"/>
+      <c r="AM4" s="148"/>
+      <c r="AN4" s="148"/>
+      <c r="AO4" s="148"/>
+      <c r="AP4" s="148"/>
+      <c r="AQ4" s="148"/>
+      <c r="AR4" s="148"/>
+      <c r="AS4" s="148"/>
+      <c r="AT4" s="149"/>
+      <c r="AU4" s="158"/>
+      <c r="AV4" s="148"/>
+      <c r="AW4" s="148"/>
+      <c r="AX4" s="148"/>
+      <c r="AY4" s="148"/>
+      <c r="AZ4" s="148"/>
+      <c r="BA4" s="148"/>
+      <c r="BB4" s="148"/>
+      <c r="BC4" s="148"/>
+      <c r="BD4" s="148"/>
+      <c r="BE4" s="148"/>
+      <c r="BF4" s="148"/>
+      <c r="BG4" s="148"/>
+      <c r="BH4" s="148"/>
+      <c r="BI4" s="148"/>
+      <c r="BJ4" s="148"/>
+      <c r="BK4" s="148"/>
+      <c r="BL4" s="148"/>
+      <c r="BM4" s="148"/>
+      <c r="BN4" s="148"/>
+      <c r="BO4" s="148"/>
+      <c r="BP4" s="148"/>
+      <c r="BQ4" s="148"/>
+      <c r="BR4" s="148"/>
+      <c r="BS4" s="148"/>
+      <c r="BT4" s="148"/>
+      <c r="BU4" s="148"/>
+      <c r="BV4" s="159"/>
+      <c r="BW4" s="148"/>
+      <c r="BX4" s="148"/>
+      <c r="BY4" s="148"/>
+      <c r="BZ4" s="148"/>
+      <c r="CA4" s="148"/>
+      <c r="CB4" s="148"/>
+      <c r="CC4" s="148"/>
+      <c r="CD4" s="148"/>
+      <c r="CE4" s="148"/>
+      <c r="CF4" s="148"/>
+      <c r="CG4" s="148"/>
+      <c r="CH4" s="148"/>
+      <c r="CI4" s="148"/>
+      <c r="CJ4" s="148"/>
+      <c r="CK4" s="148"/>
+      <c r="CL4" s="148"/>
+      <c r="CM4" s="148"/>
+      <c r="CN4" s="148"/>
+      <c r="CO4" s="148"/>
+      <c r="CP4" s="148"/>
+      <c r="CQ4" s="148"/>
+      <c r="CR4" s="149"/>
+      <c r="CS4" s="136"/>
+      <c r="CT4" s="137"/>
+      <c r="CU4" s="137"/>
+      <c r="CV4" s="137"/>
+      <c r="CW4" s="138"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="175" t="s">
+      <c r="CY4" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="176"/>
-      <c r="DA4" s="177" t="s">
+      <c r="CZ4" s="154"/>
+      <c r="DA4" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="178"/>
-      <c r="DC4" s="178"/>
-      <c r="DD4" s="178"/>
-      <c r="DE4" s="178"/>
-      <c r="DF4" s="178"/>
-      <c r="DG4" s="176"/>
+      <c r="DB4" s="156"/>
+      <c r="DC4" s="156"/>
+      <c r="DD4" s="156"/>
+      <c r="DE4" s="156"/>
+      <c r="DF4" s="156"/>
+      <c r="DG4" s="154"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="175" t="s">
+      <c r="DJ4" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="176"/>
-      <c r="DL4" s="177" t="s">
+      <c r="DK4" s="154"/>
+      <c r="DL4" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="178"/>
-      <c r="DN4" s="178"/>
-      <c r="DO4" s="178"/>
-      <c r="DP4" s="178"/>
-      <c r="DQ4" s="178"/>
-      <c r="DR4" s="176"/>
+      <c r="DM4" s="156"/>
+      <c r="DN4" s="156"/>
+      <c r="DO4" s="156"/>
+      <c r="DP4" s="156"/>
+      <c r="DQ4" s="156"/>
+      <c r="DR4" s="154"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5303,112 +5303,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="156" t="str">
+      <c r="B5" s="132"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="197" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO GENERAL SANTADER</v>
       </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="149"/>
-      <c r="Q5" s="150"/>
-      <c r="R5" s="150"/>
-      <c r="S5" s="150"/>
-      <c r="T5" s="149"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="150"/>
-      <c r="W5" s="153"/>
-      <c r="X5" s="149"/>
-      <c r="Y5" s="150"/>
-      <c r="Z5" s="150"/>
-      <c r="AA5" s="150"/>
-      <c r="AB5" s="149"/>
-      <c r="AC5" s="150"/>
-      <c r="AD5" s="150"/>
-      <c r="AE5" s="150"/>
-      <c r="AF5" s="150"/>
-      <c r="AG5" s="150"/>
-      <c r="AH5" s="150"/>
-      <c r="AI5" s="150"/>
-      <c r="AJ5" s="150"/>
-      <c r="AK5" s="153"/>
-      <c r="AL5" s="149"/>
-      <c r="AM5" s="150"/>
-      <c r="AN5" s="150"/>
-      <c r="AO5" s="150"/>
-      <c r="AP5" s="150"/>
-      <c r="AQ5" s="150"/>
-      <c r="AR5" s="150"/>
-      <c r="AS5" s="150"/>
-      <c r="AT5" s="153"/>
-      <c r="AU5" s="149"/>
-      <c r="AV5" s="150"/>
-      <c r="AW5" s="150"/>
-      <c r="AX5" s="150"/>
-      <c r="AY5" s="150"/>
-      <c r="AZ5" s="150"/>
-      <c r="BA5" s="150"/>
-      <c r="BB5" s="150"/>
-      <c r="BC5" s="150"/>
-      <c r="BD5" s="150"/>
-      <c r="BE5" s="150"/>
-      <c r="BF5" s="150"/>
-      <c r="BG5" s="150"/>
-      <c r="BH5" s="150"/>
-      <c r="BI5" s="150"/>
-      <c r="BJ5" s="150"/>
-      <c r="BK5" s="150"/>
-      <c r="BL5" s="150"/>
-      <c r="BM5" s="150"/>
-      <c r="BN5" s="150"/>
-      <c r="BO5" s="150"/>
-      <c r="BP5" s="150"/>
-      <c r="BQ5" s="150"/>
-      <c r="BR5" s="150"/>
-      <c r="BS5" s="150"/>
-      <c r="BT5" s="150"/>
-      <c r="BU5" s="150"/>
-      <c r="BV5" s="149"/>
-      <c r="BW5" s="150"/>
-      <c r="BX5" s="150"/>
-      <c r="BY5" s="150"/>
-      <c r="BZ5" s="150"/>
-      <c r="CA5" s="150"/>
-      <c r="CB5" s="150"/>
-      <c r="CC5" s="150"/>
-      <c r="CD5" s="150"/>
-      <c r="CE5" s="150"/>
-      <c r="CF5" s="150"/>
-      <c r="CG5" s="150"/>
-      <c r="CH5" s="150"/>
-      <c r="CI5" s="150"/>
-      <c r="CJ5" s="150"/>
-      <c r="CK5" s="150"/>
-      <c r="CL5" s="150"/>
-      <c r="CM5" s="150"/>
-      <c r="CN5" s="150"/>
-      <c r="CO5" s="150"/>
-      <c r="CP5" s="150"/>
-      <c r="CQ5" s="150"/>
-      <c r="CR5" s="153"/>
-      <c r="CS5" s="149"/>
-      <c r="CT5" s="150"/>
-      <c r="CU5" s="150"/>
-      <c r="CV5" s="150"/>
-      <c r="CW5" s="153"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="139"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+      <c r="W5" s="141"/>
+      <c r="X5" s="139"/>
+      <c r="Y5" s="140"/>
+      <c r="Z5" s="140"/>
+      <c r="AA5" s="140"/>
+      <c r="AB5" s="139"/>
+      <c r="AC5" s="140"/>
+      <c r="AD5" s="140"/>
+      <c r="AE5" s="140"/>
+      <c r="AF5" s="140"/>
+      <c r="AG5" s="140"/>
+      <c r="AH5" s="140"/>
+      <c r="AI5" s="140"/>
+      <c r="AJ5" s="140"/>
+      <c r="AK5" s="141"/>
+      <c r="AL5" s="139"/>
+      <c r="AM5" s="140"/>
+      <c r="AN5" s="140"/>
+      <c r="AO5" s="140"/>
+      <c r="AP5" s="140"/>
+      <c r="AQ5" s="140"/>
+      <c r="AR5" s="140"/>
+      <c r="AS5" s="140"/>
+      <c r="AT5" s="141"/>
+      <c r="AU5" s="139"/>
+      <c r="AV5" s="140"/>
+      <c r="AW5" s="140"/>
+      <c r="AX5" s="140"/>
+      <c r="AY5" s="140"/>
+      <c r="AZ5" s="140"/>
+      <c r="BA5" s="140"/>
+      <c r="BB5" s="140"/>
+      <c r="BC5" s="140"/>
+      <c r="BD5" s="140"/>
+      <c r="BE5" s="140"/>
+      <c r="BF5" s="140"/>
+      <c r="BG5" s="140"/>
+      <c r="BH5" s="140"/>
+      <c r="BI5" s="140"/>
+      <c r="BJ5" s="140"/>
+      <c r="BK5" s="140"/>
+      <c r="BL5" s="140"/>
+      <c r="BM5" s="140"/>
+      <c r="BN5" s="140"/>
+      <c r="BO5" s="140"/>
+      <c r="BP5" s="140"/>
+      <c r="BQ5" s="140"/>
+      <c r="BR5" s="140"/>
+      <c r="BS5" s="140"/>
+      <c r="BT5" s="140"/>
+      <c r="BU5" s="140"/>
+      <c r="BV5" s="139"/>
+      <c r="BW5" s="140"/>
+      <c r="BX5" s="140"/>
+      <c r="BY5" s="140"/>
+      <c r="BZ5" s="140"/>
+      <c r="CA5" s="140"/>
+      <c r="CB5" s="140"/>
+      <c r="CC5" s="140"/>
+      <c r="CD5" s="140"/>
+      <c r="CE5" s="140"/>
+      <c r="CF5" s="140"/>
+      <c r="CG5" s="140"/>
+      <c r="CH5" s="140"/>
+      <c r="CI5" s="140"/>
+      <c r="CJ5" s="140"/>
+      <c r="CK5" s="140"/>
+      <c r="CL5" s="140"/>
+      <c r="CM5" s="140"/>
+      <c r="CN5" s="140"/>
+      <c r="CO5" s="140"/>
+      <c r="CP5" s="140"/>
+      <c r="CQ5" s="140"/>
+      <c r="CR5" s="141"/>
+      <c r="CS5" s="139"/>
+      <c r="CT5" s="140"/>
+      <c r="CU5" s="140"/>
+      <c r="CV5" s="140"/>
+      <c r="CW5" s="141"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5437,11 +5437,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="182"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3414937</v>
@@ -5453,18 +5453,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="125" t="str">
+      <c r="G6" s="203" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 35</v>
       </c>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="126"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="126"/>
-      <c r="O6" s="127"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="148"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="199"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5809,41 +5809,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="179" t="s">
+      <c r="CX6" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="180"/>
-      <c r="CZ6" s="180"/>
-      <c r="DA6" s="180"/>
-      <c r="DB6" s="180"/>
-      <c r="DC6" s="180"/>
-      <c r="DD6" s="180"/>
-      <c r="DE6" s="180"/>
-      <c r="DF6" s="180"/>
-      <c r="DG6" s="180"/>
-      <c r="DH6" s="180"/>
-      <c r="DI6" s="180"/>
-      <c r="DJ6" s="180"/>
-      <c r="DK6" s="180"/>
-      <c r="DL6" s="180"/>
-      <c r="DM6" s="180"/>
-      <c r="DN6" s="180"/>
-      <c r="DO6" s="180"/>
-      <c r="DP6" s="180"/>
-      <c r="DQ6" s="180"/>
-      <c r="DR6" s="180"/>
-      <c r="DS6" s="180"/>
-      <c r="DT6" s="180"/>
-      <c r="DU6" s="180"/>
-      <c r="DV6" s="180"/>
-      <c r="DW6" s="180"/>
+      <c r="CY6" s="161"/>
+      <c r="CZ6" s="161"/>
+      <c r="DA6" s="161"/>
+      <c r="DB6" s="161"/>
+      <c r="DC6" s="161"/>
+      <c r="DD6" s="161"/>
+      <c r="DE6" s="161"/>
+      <c r="DF6" s="161"/>
+      <c r="DG6" s="161"/>
+      <c r="DH6" s="161"/>
+      <c r="DI6" s="161"/>
+      <c r="DJ6" s="161"/>
+      <c r="DK6" s="161"/>
+      <c r="DL6" s="161"/>
+      <c r="DM6" s="161"/>
+      <c r="DN6" s="161"/>
+      <c r="DO6" s="161"/>
+      <c r="DP6" s="161"/>
+      <c r="DQ6" s="161"/>
+      <c r="DR6" s="161"/>
+      <c r="DS6" s="161"/>
+      <c r="DT6" s="161"/>
+      <c r="DU6" s="161"/>
+      <c r="DV6" s="161"/>
+      <c r="DW6" s="161"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="131" t="s">
+      <c r="A7" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="124"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="182"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46084</v>
@@ -5855,15 +5855,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46086</v>
       </c>
-      <c r="G7" s="128"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="129"/>
-      <c r="O7" s="130"/>
+      <c r="G7" s="200"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="180"/>
+      <c r="J7" s="180"/>
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="201"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46084</v>
@@ -6208,58 +6208,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46380</v>
       </c>
-      <c r="CX7" s="181" t="s">
+      <c r="CX7" s="162" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="182"/>
-      <c r="CZ7" s="181" t="s">
+      <c r="CY7" s="163"/>
+      <c r="CZ7" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="180"/>
-      <c r="DB7" s="181" t="s">
+      <c r="DA7" s="161"/>
+      <c r="DB7" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="182"/>
-      <c r="DD7" s="181" t="s">
+      <c r="DC7" s="163"/>
+      <c r="DD7" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="182"/>
-      <c r="DF7" s="181" t="s">
+      <c r="DE7" s="163"/>
+      <c r="DF7" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="182"/>
-      <c r="DH7" s="181" t="s">
+      <c r="DG7" s="163"/>
+      <c r="DH7" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="182"/>
-      <c r="DJ7" s="181" t="s">
+      <c r="DI7" s="163"/>
+      <c r="DJ7" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="182"/>
-      <c r="DL7" s="181" t="s">
+      <c r="DK7" s="163"/>
+      <c r="DL7" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="182"/>
-      <c r="DN7" s="181" t="s">
+      <c r="DM7" s="163"/>
+      <c r="DN7" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="182"/>
-      <c r="DP7" s="181" t="s">
+      <c r="DO7" s="163"/>
+      <c r="DP7" s="162" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="182"/>
-      <c r="DR7" s="181" t="s">
+      <c r="DQ7" s="163"/>
+      <c r="DR7" s="162" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="182"/>
-      <c r="DT7" s="181" t="s">
+      <c r="DS7" s="163"/>
+      <c r="DT7" s="162" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="182"/>
-      <c r="DV7" s="183" t="s">
+      <c r="DU7" s="163"/>
+      <c r="DV7" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="180"/>
+      <c r="DW7" s="161"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -7354,11 +7354,11 @@
       </c>
       <c r="F12" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>CON FALTAS</v>
+        <v/>
       </c>
       <c r="G12" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="42">
         <f t="shared" si="4"/>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="I12" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="6"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="O12" s="34">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="P12" s="35" t="s">
         <v>38</v>
@@ -7419,7 +7419,7 @@
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="35" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AA12" s="35"/>
       <c r="AB12" s="35"/>
@@ -9727,19 +9727,19 @@
       <c r="DY23" s="39"/>
     </row>
     <row r="24" spans="1:129" ht="15.75" customHeight="1">
-      <c r="A24" s="215">
+      <c r="A24" s="122">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="B24" s="216" t="str">
+      <c r="B24" s="123" t="str">
         <f>'BASE DE DATOS'!C25</f>
         <v>TI</v>
       </c>
-      <c r="C24" s="217">
+      <c r="C24" s="124">
         <f>'BASE DE DATOS'!D25</f>
         <v>1087819083</v>
       </c>
-      <c r="D24" s="218" t="str">
+      <c r="D24" s="125" t="str">
         <f>'BASE DE DATOS'!B25</f>
         <v>Sharith Yesid González Rodríguez</v>
       </c>
@@ -13674,20 +13674,20 @@
       <c r="D44" s="75"/>
       <c r="E44" s="75"/>
       <c r="F44" s="74"/>
-      <c r="G44" s="132" t="s">
+      <c r="G44" s="205" t="s">
         <v>59</v>
       </c>
-      <c r="H44" s="133"/>
-      <c r="I44" s="133"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="133"/>
-      <c r="L44" s="133"/>
-      <c r="M44" s="134"/>
-      <c r="N44" s="135" t="str">
+      <c r="H44" s="166"/>
+      <c r="I44" s="166"/>
+      <c r="J44" s="166"/>
+      <c r="K44" s="166"/>
+      <c r="L44" s="166"/>
+      <c r="M44" s="167"/>
+      <c r="N44" s="168" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O44" s="136"/>
+      <c r="O44" s="169"/>
       <c r="P44" s="43">
         <f>COUNTIF(P9:P43,"A")</f>
         <v>33</v>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="Z44" s="43">
         <f t="shared" si="71"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA44" s="43">
         <f t="shared" si="71"/>
@@ -14072,20 +14072,20 @@
       <c r="D45" s="75"/>
       <c r="E45" s="75"/>
       <c r="F45" s="74"/>
-      <c r="G45" s="168" t="s">
+      <c r="G45" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="133"/>
-      <c r="I45" s="133"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="133"/>
-      <c r="L45" s="133"/>
-      <c r="M45" s="134"/>
-      <c r="N45" s="135" t="str">
+      <c r="H45" s="166"/>
+      <c r="I45" s="166"/>
+      <c r="J45" s="166"/>
+      <c r="K45" s="166"/>
+      <c r="L45" s="166"/>
+      <c r="M45" s="167"/>
+      <c r="N45" s="168" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O45" s="136"/>
+      <c r="O45" s="169"/>
       <c r="P45" s="43">
         <f>COUNTIF(P9:P43,"CE")</f>
         <v>0</v>
@@ -14470,20 +14470,20 @@
       <c r="D46" s="75"/>
       <c r="E46" s="75"/>
       <c r="F46" s="74"/>
-      <c r="G46" s="169" t="s">
+      <c r="G46" s="176" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="133"/>
-      <c r="I46" s="133"/>
-      <c r="J46" s="133"/>
-      <c r="K46" s="133"/>
-      <c r="L46" s="133"/>
-      <c r="M46" s="134"/>
-      <c r="N46" s="135" t="str">
+      <c r="H46" s="166"/>
+      <c r="I46" s="166"/>
+      <c r="J46" s="166"/>
+      <c r="K46" s="166"/>
+      <c r="L46" s="166"/>
+      <c r="M46" s="167"/>
+      <c r="N46" s="168" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O46" s="136"/>
+      <c r="O46" s="169"/>
       <c r="P46" s="43">
         <f>COUNTIF(P9:P43,"SE")</f>
         <v>2</v>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="Z46" s="43">
         <f t="shared" si="79"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA46" s="43">
         <f t="shared" si="79"/>
@@ -14868,20 +14868,20 @@
       <c r="D47" s="75"/>
       <c r="E47" s="75"/>
       <c r="F47" s="44"/>
-      <c r="G47" s="170" t="s">
+      <c r="G47" s="177" t="s">
         <v>60</v>
       </c>
-      <c r="H47" s="133"/>
-      <c r="I47" s="133"/>
-      <c r="J47" s="133"/>
-      <c r="K47" s="133"/>
-      <c r="L47" s="133"/>
-      <c r="M47" s="134"/>
-      <c r="N47" s="135" t="str">
+      <c r="H47" s="166"/>
+      <c r="I47" s="166"/>
+      <c r="J47" s="166"/>
+      <c r="K47" s="166"/>
+      <c r="L47" s="166"/>
+      <c r="M47" s="167"/>
+      <c r="N47" s="168" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O47" s="136"/>
+      <c r="O47" s="169"/>
       <c r="P47" s="43">
         <f>COUNTIF(P9:P43,"INC")</f>
         <v>0</v>
@@ -15266,20 +15266,20 @@
       <c r="D48" s="75"/>
       <c r="E48" s="75"/>
       <c r="F48" s="74"/>
-      <c r="G48" s="164" t="s">
+      <c r="G48" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="133"/>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="133"/>
-      <c r="M48" s="134"/>
-      <c r="N48" s="135" t="str">
+      <c r="H48" s="166"/>
+      <c r="I48" s="166"/>
+      <c r="J48" s="166"/>
+      <c r="K48" s="166"/>
+      <c r="L48" s="166"/>
+      <c r="M48" s="167"/>
+      <c r="N48" s="168" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O48" s="136"/>
+      <c r="O48" s="169"/>
       <c r="P48" s="43">
         <f>COUNTIF(P9:P43,"LIC")</f>
         <v>0</v>
@@ -15664,20 +15664,20 @@
       <c r="D49" s="75"/>
       <c r="E49" s="75"/>
       <c r="F49" s="74"/>
-      <c r="G49" s="172" t="s">
+      <c r="G49" s="165" t="s">
         <v>62</v>
       </c>
-      <c r="H49" s="133"/>
-      <c r="I49" s="133"/>
-      <c r="J49" s="133"/>
-      <c r="K49" s="133"/>
-      <c r="L49" s="133"/>
-      <c r="M49" s="134"/>
-      <c r="N49" s="135" t="str">
+      <c r="H49" s="166"/>
+      <c r="I49" s="166"/>
+      <c r="J49" s="166"/>
+      <c r="K49" s="166"/>
+      <c r="L49" s="166"/>
+      <c r="M49" s="167"/>
+      <c r="N49" s="168" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O49" s="136"/>
+      <c r="O49" s="169"/>
       <c r="P49" s="43">
         <f>COUNTIF(P9:P43,"CLM")</f>
         <v>0</v>
@@ -16062,20 +16062,20 @@
       <c r="D50" s="75"/>
       <c r="E50" s="75"/>
       <c r="F50" s="74"/>
-      <c r="G50" s="173" t="s">
+      <c r="G50" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="H50" s="133"/>
-      <c r="I50" s="133"/>
-      <c r="J50" s="133"/>
-      <c r="K50" s="133"/>
-      <c r="L50" s="133"/>
-      <c r="M50" s="134"/>
-      <c r="N50" s="135" t="str">
+      <c r="H50" s="166"/>
+      <c r="I50" s="166"/>
+      <c r="J50" s="166"/>
+      <c r="K50" s="166"/>
+      <c r="L50" s="166"/>
+      <c r="M50" s="167"/>
+      <c r="N50" s="168" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O50" s="136"/>
+      <c r="O50" s="169"/>
       <c r="P50" s="43">
         <f>COUNTIF(P9:P43,"SFF")</f>
         <v>0</v>
@@ -16460,20 +16460,20 @@
       <c r="D51" s="75"/>
       <c r="E51" s="75"/>
       <c r="F51" s="74"/>
-      <c r="G51" s="174" t="s">
+      <c r="G51" s="171" t="s">
         <v>64</v>
       </c>
-      <c r="H51" s="133"/>
-      <c r="I51" s="133"/>
-      <c r="J51" s="133"/>
-      <c r="K51" s="133"/>
-      <c r="L51" s="133"/>
-      <c r="M51" s="134"/>
-      <c r="N51" s="135" t="str">
+      <c r="H51" s="166"/>
+      <c r="I51" s="166"/>
+      <c r="J51" s="166"/>
+      <c r="K51" s="166"/>
+      <c r="L51" s="166"/>
+      <c r="M51" s="167"/>
+      <c r="N51" s="168" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O51" s="136"/>
+      <c r="O51" s="169"/>
       <c r="P51" s="43">
         <f>COUNTIF(P9:P43,"RET")</f>
         <v>0</v>
@@ -41814,23 +41814,53 @@
   </sheetData>
   <autoFilter ref="A8:DW51" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:BU1"/>
-    <mergeCell ref="BV1:CR1"/>
-    <mergeCell ref="AL3:AT3"/>
-    <mergeCell ref="CS1:CW5"/>
-    <mergeCell ref="AU2:BU2"/>
-    <mergeCell ref="BV2:CR2"/>
-    <mergeCell ref="BV3:CR3"/>
-    <mergeCell ref="AL2:AT2"/>
-    <mergeCell ref="AL4:AT5"/>
-    <mergeCell ref="CY1:DG1"/>
-    <mergeCell ref="CY2:DG2"/>
-    <mergeCell ref="CY4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="AU3:BU3"/>
-    <mergeCell ref="AU4:BU5"/>
-    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:O7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G44:M44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="AB1:AK1"/>
+    <mergeCell ref="AB2:AK2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G3:O3"/>
+    <mergeCell ref="G4:O5"/>
+    <mergeCell ref="P4:S5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="X4:AA5"/>
+    <mergeCell ref="AB4:AK5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="AB3:AK3"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G1:O1"/>
+    <mergeCell ref="G48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="G45:M45"/>
+    <mergeCell ref="G46:M46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="G47:M47"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="G49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="N51:O51"/>
     <mergeCell ref="DJ4:DK4"/>
     <mergeCell ref="DL4:DR4"/>
     <mergeCell ref="CX6:DW6"/>
@@ -41847,53 +41877,23 @@
     <mergeCell ref="DF7:DG7"/>
     <mergeCell ref="DH7:DI7"/>
     <mergeCell ref="DJ7:DK7"/>
-    <mergeCell ref="G49:M49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="G50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="G48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="G45:M45"/>
-    <mergeCell ref="G46:M46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="G47:M47"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="G1:O1"/>
-    <mergeCell ref="X1:AA1"/>
-    <mergeCell ref="AB1:AK1"/>
-    <mergeCell ref="AB2:AK2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G3:O3"/>
-    <mergeCell ref="G4:O5"/>
-    <mergeCell ref="P4:S5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="X4:AA5"/>
-    <mergeCell ref="AB4:AK5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="AB3:AK3"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:O7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G44:M44"/>
-    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="CY1:DG1"/>
+    <mergeCell ref="CY2:DG2"/>
+    <mergeCell ref="CY4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="AU3:BU3"/>
+    <mergeCell ref="AU4:BU5"/>
+    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="AL1:AT1"/>
+    <mergeCell ref="AU1:BU1"/>
+    <mergeCell ref="BV1:CR1"/>
+    <mergeCell ref="AL3:AT3"/>
+    <mergeCell ref="CS1:CW5"/>
+    <mergeCell ref="AU2:BU2"/>
+    <mergeCell ref="BV2:CR2"/>
+    <mergeCell ref="BV3:CR3"/>
+    <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AL4:AT5"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E43">
     <cfRule type="containsText" dxfId="80" priority="1" operator="containsText" text="RETIRADO">
@@ -42262,18 +42262,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="204">
-        <v>0</v>
-      </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="198"/>
+      <c r="A1" s="212">
+        <v>0</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="138"/>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
       <c r="N1" s="48"/>
@@ -42291,16 +42291,16 @@
       <c r="Z1" s="48"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="147"/>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="198"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="138"/>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
@@ -42318,15 +42318,15 @@
       <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:26" ht="15.75">
-      <c r="A3" s="202" t="s">
+      <c r="A3" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="205" t="s">
+      <c r="B3" s="182"/>
+      <c r="C3" s="213" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="182"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="50"/>
@@ -42350,15 +42350,15 @@
       <c r="Z3" s="48"/>
     </row>
     <row r="4" spans="1:26" ht="15.75">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="206" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="124"/>
-      <c r="C4" s="206">
+      <c r="B4" s="182"/>
+      <c r="C4" s="214">
         <v>3414937</v>
       </c>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="182"/>
       <c r="F4" s="51" t="s">
         <v>65</v>
       </c>
@@ -42388,15 +42388,15 @@
       <c r="Z4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15.75">
-      <c r="A5" s="202" t="s">
+      <c r="A5" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="124"/>
-      <c r="C5" s="203" t="s">
+      <c r="B5" s="182"/>
+      <c r="C5" s="211" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="123"/>
-      <c r="E5" s="124"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="182"/>
       <c r="F5" s="51" t="s">
         <v>67</v>
       </c>
@@ -42424,15 +42424,15 @@
       <c r="Z5" s="48"/>
     </row>
     <row r="6" spans="1:26" ht="15.75">
-      <c r="A6" s="202" t="s">
+      <c r="A6" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="124"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="207" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="123"/>
-      <c r="E6" s="124"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="182"/>
       <c r="F6" s="51" t="s">
         <v>69</v>
       </c>
@@ -42460,15 +42460,15 @@
       <c r="Z6" s="48"/>
     </row>
     <row r="7" spans="1:26" ht="15.75">
-      <c r="A7" s="202" t="s">
+      <c r="A7" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="124"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="208" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="182"/>
       <c r="F7" s="55" t="s">
         <v>70</v>
       </c>
@@ -42499,14 +42499,14 @@
       <c r="A8" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="124"/>
+      <c r="B8" s="182"/>
       <c r="C8" s="210" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="124"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="182"/>
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="48"/>
@@ -52921,12 +52921,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A1:J2"/>
@@ -52934,6 +52928,12 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="B45:B49">
     <cfRule type="expression" dxfId="15" priority="1">
@@ -53134,12 +53134,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
       <c r="E1" s="62"/>
       <c r="F1" s="62"/>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="212" t="s">
+      <c r="A3" s="215" t="s">
         <v>356</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -53172,7 +53172,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="213"/>
+      <c r="A4" s="216"/>
       <c r="B4" s="66" t="s">
         <v>278</v>
       </c>
@@ -53184,7 +53184,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="213"/>
+      <c r="A5" s="216"/>
       <c r="B5" s="66" t="s">
         <v>280</v>
       </c>
@@ -53196,7 +53196,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="213"/>
+      <c r="A6" s="216"/>
       <c r="B6" s="66" t="s">
         <v>282</v>
       </c>
@@ -53208,7 +53208,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="214"/>
+      <c r="A7" s="217"/>
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
       <c r="D7" s="69"/>
@@ -53231,7 +53231,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="212" t="s">
+      <c r="A10" s="215" t="s">
         <v>357</v>
       </c>
       <c r="B10" s="66" t="s">
@@ -53245,7 +53245,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="213"/>
+      <c r="A11" s="216"/>
       <c r="B11" s="66" t="s">
         <v>286</v>
       </c>
@@ -53257,7 +53257,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="213"/>
+      <c r="A12" s="216"/>
       <c r="B12" s="66" t="s">
         <v>291</v>
       </c>
@@ -53269,13 +53269,13 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="213"/>
+      <c r="A13" s="216"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="113"/>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="214"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="68"/>
       <c r="C14" s="68"/>
       <c r="D14" s="69"/>
@@ -53295,7 +53295,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="212" t="s">
+      <c r="A17" s="215" t="s">
         <v>358</v>
       </c>
       <c r="B17" s="66" t="s">
@@ -53309,7 +53309,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="213"/>
+      <c r="A18" s="216"/>
       <c r="B18" s="66" t="s">
         <v>295</v>
       </c>
@@ -53321,7 +53321,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="213"/>
+      <c r="A19" s="216"/>
       <c r="B19" s="66" t="s">
         <v>297</v>
       </c>
@@ -53333,7 +53333,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="213"/>
+      <c r="A20" s="216"/>
       <c r="B20" s="66" t="s">
         <v>299</v>
       </c>
@@ -53345,7 +53345,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="214"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68"/>
       <c r="D21" s="69"/>
@@ -53365,7 +53365,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="212" t="s">
+      <c r="A24" s="215" t="s">
         <v>359</v>
       </c>
       <c r="B24" s="66" t="s">
@@ -53379,7 +53379,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="213"/>
+      <c r="A25" s="216"/>
       <c r="B25" s="66" t="s">
         <v>304</v>
       </c>
@@ -53391,7 +53391,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="213"/>
+      <c r="A26" s="216"/>
       <c r="B26" s="66" t="s">
         <v>306</v>
       </c>
@@ -53403,7 +53403,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="213"/>
+      <c r="A27" s="216"/>
       <c r="B27" s="66" t="s">
         <v>307</v>
       </c>
@@ -53415,7 +53415,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="214"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
       <c r="D28" s="69"/>
@@ -53435,7 +53435,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="212" t="s">
+      <c r="A31" s="215" t="s">
         <v>360</v>
       </c>
       <c r="B31" s="66" t="s">
@@ -53449,7 +53449,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="213"/>
+      <c r="A32" s="216"/>
       <c r="B32" s="66" t="s">
         <v>311</v>
       </c>
@@ -53461,7 +53461,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="213"/>
+      <c r="A33" s="216"/>
       <c r="B33" s="66" t="s">
         <v>313</v>
       </c>
@@ -53473,7 +53473,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="213"/>
+      <c r="A34" s="216"/>
       <c r="B34" s="66" t="s">
         <v>315</v>
       </c>
@@ -53485,7 +53485,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="214"/>
+      <c r="A35" s="217"/>
       <c r="B35" s="68"/>
       <c r="C35" s="68"/>
       <c r="D35" s="69"/>
@@ -53505,7 +53505,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="212" t="s">
+      <c r="A38" s="215" t="s">
         <v>361</v>
       </c>
       <c r="B38" s="66" t="s">
@@ -53519,7 +53519,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="213"/>
+      <c r="A39" s="216"/>
       <c r="B39" s="66" t="s">
         <v>319</v>
       </c>
@@ -53531,7 +53531,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="213"/>
+      <c r="A40" s="216"/>
       <c r="B40" s="66" t="s">
         <v>320</v>
       </c>
@@ -53543,7 +53543,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="213"/>
+      <c r="A41" s="216"/>
       <c r="B41" s="66" t="s">
         <v>288</v>
       </c>
@@ -53555,7 +53555,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="214"/>
+      <c r="A42" s="217"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
       <c r="D42" s="69"/>
@@ -53576,7 +53576,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
-      <c r="A45" s="212" t="s">
+      <c r="A45" s="215" t="s">
         <v>362</v>
       </c>
       <c r="B45" s="66" t="s">
@@ -53590,7 +53590,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="213"/>
+      <c r="A46" s="216"/>
       <c r="B46" s="66" t="s">
         <v>324</v>
       </c>
@@ -53602,7 +53602,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="213"/>
+      <c r="A47" s="216"/>
       <c r="B47" s="66" t="s">
         <v>326</v>
       </c>
@@ -53614,7 +53614,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="213"/>
+      <c r="A48" s="216"/>
       <c r="B48" s="66" t="s">
         <v>328</v>
       </c>
@@ -53626,7 +53626,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="214"/>
+      <c r="A49" s="217"/>
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
       <c r="D49" s="69"/>
@@ -53647,7 +53647,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
-      <c r="A52" s="212" t="s">
+      <c r="A52" s="215" t="s">
         <v>363</v>
       </c>
       <c r="B52" s="66" t="s">
@@ -53661,7 +53661,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
-      <c r="A53" s="213"/>
+      <c r="A53" s="216"/>
       <c r="B53" s="66" t="s">
         <v>332</v>
       </c>
@@ -53673,7 +53673,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
-      <c r="A54" s="213"/>
+      <c r="A54" s="216"/>
       <c r="B54" s="66" t="s">
         <v>334</v>
       </c>
@@ -53685,7 +53685,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
-      <c r="A55" s="213"/>
+      <c r="A55" s="216"/>
       <c r="B55" s="66" t="s">
         <v>336</v>
       </c>
@@ -53697,7 +53697,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="214"/>
+      <c r="A56" s="217"/>
       <c r="B56" s="68" t="s">
         <v>339</v>
       </c>
@@ -53724,7 +53724,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="212" t="s">
+      <c r="A59" s="215" t="s">
         <v>364</v>
       </c>
       <c r="B59" s="66" t="s">
@@ -53738,7 +53738,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1">
-      <c r="A60" s="213"/>
+      <c r="A60" s="216"/>
       <c r="B60" s="66" t="s">
         <v>345</v>
       </c>
@@ -53750,35 +53750,35 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1">
-      <c r="A61" s="213"/>
+      <c r="A61" s="216"/>
       <c r="B61" s="66"/>
       <c r="C61" s="66"/>
       <c r="D61" s="113"/>
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1">
-      <c r="A62" s="213"/>
+      <c r="A62" s="216"/>
       <c r="B62" s="66"/>
       <c r="C62" s="66"/>
       <c r="D62" s="67"/>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="214"/>
+      <c r="A63" s="217"/>
       <c r="B63" s="68"/>
       <c r="C63" s="68"/>
       <c r="D63" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A24:A28"/>
     <mergeCell ref="A45:A49"/>
     <mergeCell ref="A52:A56"/>
     <mergeCell ref="A59:A63"/>
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="A38:A42"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A24:A28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{BF44E5AF-C41E-4FE1-AB09-EC39BA924783}"/>
